--- a/data/uploads_local/공모펀드_판매대본_JPMorgan.xlsx
+++ b/data/uploads_local/공모펀드_판매대본_JPMorgan.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/a114384/Desktop/2.KISAI/펀드 불완전판매/data/uploads_local/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B7C688BA-1C54-1C4C-BBA8-83A8170BD85D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D6A2320-6BA4-824A-83EA-A9FF7F561D82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="31940" windowHeight="19200" tabRatio="813" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -8989,9 +8989,282 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="5" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="49" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="69" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="25" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9001,27 +9274,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9040,15 +9292,6 @@
     <xf numFmtId="0" fontId="31" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="5" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="31" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -9061,263 +9304,20 @@
     <xf numFmtId="0" fontId="31" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="33" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="33" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="69" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="4" xfId="7" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="3" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="5" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="2" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="7" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="4" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="49" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="7" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="9">
@@ -9887,35 +9887,35 @@
       <c r="C4" s="1"/>
     </row>
     <row r="5" spans="1:11" ht="34.5" customHeight="1">
-      <c r="A5" s="229" t="s">
+      <c r="A5" s="226" t="s">
         <v>22</v>
       </c>
-      <c r="B5" s="229"/>
-      <c r="C5" s="229" t="s">
+      <c r="B5" s="226"/>
+      <c r="C5" s="226" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="229" t="s">
+      <c r="D5" s="226" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="229"/>
-      <c r="F5" s="229" t="s">
+      <c r="E5" s="226"/>
+      <c r="F5" s="226" t="s">
         <v>8</v>
       </c>
-      <c r="G5" s="229"/>
-      <c r="H5" s="231" t="s">
+      <c r="G5" s="226"/>
+      <c r="H5" s="250" t="s">
         <v>9</v>
       </c>
-      <c r="I5" s="229" t="s">
+      <c r="I5" s="226" t="s">
         <v>2</v>
       </c>
-      <c r="J5" s="229" t="s">
+      <c r="J5" s="226" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="34.5" customHeight="1">
-      <c r="A6" s="229"/>
-      <c r="B6" s="229"/>
-      <c r="C6" s="229"/>
+      <c r="A6" s="226"/>
+      <c r="B6" s="226"/>
+      <c r="C6" s="226"/>
       <c r="D6" s="82" t="s">
         <v>3</v>
       </c>
@@ -9928,34 +9928,34 @@
       <c r="G6" s="82" t="s">
         <v>4</v>
       </c>
-      <c r="H6" s="231"/>
-      <c r="I6" s="229"/>
-      <c r="J6" s="229"/>
+      <c r="H6" s="250"/>
+      <c r="I6" s="226"/>
+      <c r="J6" s="226"/>
     </row>
     <row r="7" spans="1:11" ht="67.5" customHeight="1">
-      <c r="A7" s="211" t="s">
+      <c r="A7" s="227" t="s">
         <v>15</v>
       </c>
-      <c r="B7" s="212"/>
-      <c r="C7" s="221" t="s">
+      <c r="B7" s="190"/>
+      <c r="C7" s="246" t="s">
         <v>226</v>
       </c>
-      <c r="D7" s="217" t="s">
+      <c r="D7" s="182" t="s">
         <v>212</v>
       </c>
-      <c r="E7" s="217" t="s">
+      <c r="E7" s="182" t="s">
         <v>212</v>
       </c>
-      <c r="F7" s="217" t="s">
+      <c r="F7" s="182" t="s">
         <v>212</v>
       </c>
-      <c r="G7" s="217" t="s">
+      <c r="G7" s="182" t="s">
         <v>212</v>
       </c>
-      <c r="H7" s="217" t="s">
+      <c r="H7" s="182" t="s">
         <v>212</v>
       </c>
-      <c r="I7" s="184" t="s">
+      <c r="I7" s="201" t="s">
         <v>213</v>
       </c>
       <c r="J7" s="83" t="s">
@@ -9963,55 +9963,55 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A8" s="219"/>
-      <c r="B8" s="220"/>
-      <c r="C8" s="222"/>
-      <c r="D8" s="224"/>
-      <c r="E8" s="224"/>
-      <c r="F8" s="224"/>
-      <c r="G8" s="224"/>
-      <c r="H8" s="224"/>
-      <c r="I8" s="230"/>
+      <c r="A8" s="257"/>
+      <c r="B8" s="192"/>
+      <c r="C8" s="258"/>
+      <c r="D8" s="248"/>
+      <c r="E8" s="248"/>
+      <c r="F8" s="248"/>
+      <c r="G8" s="248"/>
+      <c r="H8" s="248"/>
+      <c r="I8" s="249"/>
       <c r="J8" s="84" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="90.75" customHeight="1">
-      <c r="A9" s="213"/>
-      <c r="B9" s="214"/>
-      <c r="C9" s="223"/>
-      <c r="D9" s="218"/>
-      <c r="E9" s="218"/>
-      <c r="F9" s="218"/>
-      <c r="G9" s="218"/>
-      <c r="H9" s="218"/>
-      <c r="I9" s="185"/>
+      <c r="A9" s="228"/>
+      <c r="B9" s="229"/>
+      <c r="C9" s="247"/>
+      <c r="D9" s="183"/>
+      <c r="E9" s="183"/>
+      <c r="F9" s="183"/>
+      <c r="G9" s="183"/>
+      <c r="H9" s="183"/>
+      <c r="I9" s="202"/>
       <c r="J9" s="85" t="s">
         <v>227</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="60.75" customHeight="1">
-      <c r="A10" s="211" t="s">
+      <c r="A10" s="227" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="212"/>
-      <c r="C10" s="215" t="s">
+      <c r="B10" s="190"/>
+      <c r="C10" s="255" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="217" t="s">
+      <c r="D10" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="E10" s="217" t="s">
+      <c r="E10" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="F10" s="217" t="s">
+      <c r="F10" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="G10" s="217" t="s">
+      <c r="G10" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="H10" s="232"/>
-      <c r="I10" s="234" t="s">
+      <c r="H10" s="251"/>
+      <c r="I10" s="253" t="s">
         <v>228</v>
       </c>
       <c r="J10" s="86" t="s">
@@ -10020,65 +10020,65 @@
       <c r="K10" s="81"/>
     </row>
     <row r="11" spans="1:11" ht="16.5" customHeight="1">
-      <c r="A11" s="213"/>
-      <c r="B11" s="214"/>
-      <c r="C11" s="216"/>
-      <c r="D11" s="218"/>
-      <c r="E11" s="218"/>
-      <c r="F11" s="218"/>
-      <c r="G11" s="218"/>
-      <c r="H11" s="233"/>
-      <c r="I11" s="235"/>
+      <c r="A11" s="228"/>
+      <c r="B11" s="229"/>
+      <c r="C11" s="256"/>
+      <c r="D11" s="183"/>
+      <c r="E11" s="183"/>
+      <c r="F11" s="183"/>
+      <c r="G11" s="183"/>
+      <c r="H11" s="252"/>
+      <c r="I11" s="254"/>
       <c r="J11" s="84" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:11" ht="60.75" hidden="1" customHeight="1">
-      <c r="A12" s="211" t="s">
+      <c r="A12" s="227" t="s">
         <v>216</v>
       </c>
-      <c r="B12" s="212"/>
-      <c r="C12" s="221"/>
-      <c r="D12" s="217" t="s">
+      <c r="B12" s="190"/>
+      <c r="C12" s="246"/>
+      <c r="D12" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="E12" s="217" t="s">
+      <c r="E12" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="F12" s="217" t="s">
+      <c r="F12" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="G12" s="217" t="s">
+      <c r="G12" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="H12" s="217" t="s">
+      <c r="H12" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="I12" s="184"/>
+      <c r="I12" s="201"/>
       <c r="J12" s="87" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="13" spans="1:11" ht="16.5" hidden="1" customHeight="1">
-      <c r="A13" s="213"/>
-      <c r="B13" s="214"/>
-      <c r="C13" s="223"/>
-      <c r="D13" s="218"/>
-      <c r="E13" s="218"/>
-      <c r="F13" s="218"/>
-      <c r="G13" s="218"/>
-      <c r="H13" s="218"/>
-      <c r="I13" s="185"/>
+      <c r="A13" s="228"/>
+      <c r="B13" s="229"/>
+      <c r="C13" s="247"/>
+      <c r="D13" s="183"/>
+      <c r="E13" s="183"/>
+      <c r="F13" s="183"/>
+      <c r="G13" s="183"/>
+      <c r="H13" s="183"/>
+      <c r="I13" s="202"/>
       <c r="J13" s="88" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="14" spans="1:11" ht="57" customHeight="1">
-      <c r="A14" s="186" t="s">
+      <c r="A14" s="270" t="s">
         <v>356</v>
       </c>
-      <c r="B14" s="187"/>
-      <c r="C14" s="221" t="s">
+      <c r="B14" s="271"/>
+      <c r="C14" s="246" t="s">
         <v>313</v>
       </c>
       <c r="D14" s="89"/>
@@ -10086,7 +10086,7 @@
       <c r="F14" s="89"/>
       <c r="G14" s="89"/>
       <c r="H14" s="89"/>
-      <c r="I14" s="184" t="s">
+      <c r="I14" s="201" t="s">
         <v>222</v>
       </c>
       <c r="J14" s="163" t="s">
@@ -10094,22 +10094,22 @@
       </c>
     </row>
     <row r="15" spans="1:11" ht="102.75" customHeight="1">
-      <c r="A15" s="188"/>
-      <c r="B15" s="189"/>
-      <c r="C15" s="223"/>
+      <c r="A15" s="272"/>
+      <c r="B15" s="273"/>
+      <c r="C15" s="247"/>
       <c r="D15" s="89"/>
       <c r="E15" s="89"/>
       <c r="F15" s="89"/>
       <c r="G15" s="89"/>
       <c r="H15" s="89"/>
-      <c r="I15" s="185"/>
+      <c r="I15" s="202"/>
       <c r="J15" s="164" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:11" ht="114" customHeight="1">
-      <c r="A16" s="190"/>
-      <c r="B16" s="191"/>
+      <c r="A16" s="274"/>
+      <c r="B16" s="275"/>
       <c r="C16" s="159" t="s">
         <v>312</v>
       </c>
@@ -10124,10 +10124,10 @@
       </c>
     </row>
     <row r="17" spans="1:10" ht="57.75" customHeight="1">
-      <c r="A17" s="197" t="s">
+      <c r="A17" s="278" t="s">
         <v>231</v>
       </c>
-      <c r="B17" s="198"/>
+      <c r="B17" s="279"/>
       <c r="C17" s="160" t="s">
         <v>218</v>
       </c>
@@ -10142,10 +10142,10 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="78.75" customHeight="1">
-      <c r="A18" s="186" t="s">
+      <c r="A18" s="270" t="s">
         <v>357</v>
       </c>
-      <c r="B18" s="187"/>
+      <c r="B18" s="271"/>
       <c r="C18" s="158" t="s">
         <v>219</v>
       </c>
@@ -10160,8 +10160,8 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="171.75" customHeight="1">
-      <c r="A19" s="188"/>
-      <c r="B19" s="189"/>
+      <c r="A19" s="272"/>
+      <c r="B19" s="273"/>
       <c r="C19" s="158" t="s">
         <v>220</v>
       </c>
@@ -10178,8 +10178,8 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A20" s="188"/>
-      <c r="B20" s="189"/>
+      <c r="A20" s="272"/>
+      <c r="B20" s="273"/>
       <c r="C20" s="158"/>
       <c r="D20" s="93"/>
       <c r="E20" s="93"/>
@@ -10192,10 +10192,10 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="51.75" customHeight="1" thickBot="1">
-      <c r="A21" s="195" t="s">
+      <c r="A21" s="276" t="s">
         <v>358</v>
       </c>
-      <c r="B21" s="196"/>
+      <c r="B21" s="277"/>
       <c r="C21" s="161" t="s">
         <v>221</v>
       </c>
@@ -10210,17 +10210,17 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="90.75" customHeight="1" thickTop="1">
-      <c r="A22" s="192" t="s">
+      <c r="A22" s="260" t="s">
         <v>16</v>
       </c>
-      <c r="B22" s="192"/>
+      <c r="B22" s="260"/>
       <c r="C22" s="157"/>
       <c r="D22" s="152"/>
       <c r="E22" s="152"/>
       <c r="F22" s="152"/>
       <c r="G22" s="152"/>
       <c r="H22" s="152"/>
-      <c r="I22" s="193" t="s">
+      <c r="I22" s="181" t="s">
         <v>352</v>
       </c>
       <c r="J22" s="57" t="s">
@@ -10228,37 +10228,37 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="164.25" customHeight="1">
-      <c r="A23" s="192"/>
-      <c r="B23" s="192"/>
+      <c r="A23" s="260"/>
+      <c r="B23" s="260"/>
       <c r="C23" s="157"/>
       <c r="D23" s="152"/>
       <c r="E23" s="152"/>
       <c r="F23" s="152"/>
       <c r="G23" s="152"/>
       <c r="H23" s="152"/>
-      <c r="I23" s="193"/>
+      <c r="I23" s="181"/>
       <c r="J23" s="40" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="58.5" customHeight="1">
-      <c r="A24" s="229" t="s">
+      <c r="A24" s="226" t="s">
         <v>271</v>
       </c>
-      <c r="B24" s="192" t="s">
+      <c r="B24" s="260" t="s">
         <v>270</v>
       </c>
-      <c r="C24" s="202" t="s">
+      <c r="C24" s="197" t="s">
         <v>129</v>
       </c>
-      <c r="D24" s="199" t="s">
+      <c r="D24" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="E24" s="194"/>
-      <c r="F24" s="194"/>
-      <c r="G24" s="194"/>
-      <c r="H24" s="194"/>
-      <c r="I24" s="208" t="s">
+      <c r="E24" s="176"/>
+      <c r="F24" s="176"/>
+      <c r="G24" s="176"/>
+      <c r="H24" s="176"/>
+      <c r="I24" s="178" t="s">
         <v>239</v>
       </c>
       <c r="J24" s="41" t="s">
@@ -10266,36 +10266,36 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="29.25" customHeight="1">
-      <c r="A25" s="229"/>
-      <c r="B25" s="192"/>
-      <c r="C25" s="202"/>
-      <c r="D25" s="199"/>
-      <c r="E25" s="194"/>
-      <c r="F25" s="194"/>
-      <c r="G25" s="194"/>
-      <c r="H25" s="194"/>
-      <c r="I25" s="208"/>
+      <c r="A25" s="226"/>
+      <c r="B25" s="260"/>
+      <c r="C25" s="197"/>
+      <c r="D25" s="175"/>
+      <c r="E25" s="176"/>
+      <c r="F25" s="176"/>
+      <c r="G25" s="176"/>
+      <c r="H25" s="176"/>
+      <c r="I25" s="178"/>
       <c r="J25" s="42" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="73.5" customHeight="1">
-      <c r="A26" s="229"/>
-      <c r="B26" s="192"/>
-      <c r="C26" s="202"/>
-      <c r="D26" s="199"/>
-      <c r="E26" s="194"/>
-      <c r="F26" s="194"/>
-      <c r="G26" s="194"/>
-      <c r="H26" s="194"/>
-      <c r="I26" s="208"/>
+      <c r="A26" s="226"/>
+      <c r="B26" s="260"/>
+      <c r="C26" s="197"/>
+      <c r="D26" s="175"/>
+      <c r="E26" s="176"/>
+      <c r="F26" s="176"/>
+      <c r="G26" s="176"/>
+      <c r="H26" s="176"/>
+      <c r="I26" s="178"/>
       <c r="J26" s="41" t="s">
         <v>318</v>
       </c>
     </row>
     <row r="27" spans="1:10" ht="96" customHeight="1">
-      <c r="A27" s="229"/>
-      <c r="B27" s="227" t="s">
+      <c r="A27" s="226"/>
+      <c r="B27" s="259" t="s">
         <v>19</v>
       </c>
       <c r="C27" s="74" t="s">
@@ -10318,8 +10318,8 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="75.75" customHeight="1">
-      <c r="A28" s="229"/>
-      <c r="B28" s="227"/>
+      <c r="A28" s="226"/>
+      <c r="B28" s="259"/>
       <c r="C28" s="74" t="s">
         <v>51</v>
       </c>
@@ -10340,8 +10340,8 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="45.75" customHeight="1">
-      <c r="A29" s="229"/>
-      <c r="B29" s="227"/>
+      <c r="A29" s="226"/>
+      <c r="B29" s="259"/>
       <c r="C29" s="74" t="s">
         <v>129</v>
       </c>
@@ -10360,13 +10360,13 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="65.25" customHeight="1">
-      <c r="A30" s="207" t="s">
+      <c r="A30" s="177" t="s">
         <v>59</v>
       </c>
       <c r="B30" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="C30" s="228" t="s">
+      <c r="C30" s="232" t="s">
         <v>78</v>
       </c>
       <c r="D30" s="91" t="s">
@@ -10392,24 +10392,24 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="90">
-      <c r="A31" s="207"/>
-      <c r="B31" s="207" t="s">
+      <c r="A31" s="177"/>
+      <c r="B31" s="177" t="s">
         <v>64</v>
       </c>
-      <c r="C31" s="228"/>
-      <c r="D31" s="199" t="s">
+      <c r="C31" s="232"/>
+      <c r="D31" s="175" t="s">
         <v>241</v>
       </c>
-      <c r="E31" s="199" t="s">
+      <c r="E31" s="175" t="s">
         <v>241</v>
       </c>
-      <c r="F31" s="199" t="s">
+      <c r="F31" s="175" t="s">
         <v>241</v>
       </c>
-      <c r="G31" s="199" t="s">
+      <c r="G31" s="175" t="s">
         <v>241</v>
       </c>
-      <c r="H31" s="194" t="s">
+      <c r="H31" s="176" t="s">
         <v>62</v>
       </c>
       <c r="I31" s="104" t="s">
@@ -10420,14 +10420,14 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="49.5" customHeight="1">
-      <c r="A32" s="207"/>
-      <c r="B32" s="207"/>
-      <c r="C32" s="228"/>
-      <c r="D32" s="199"/>
-      <c r="E32" s="199"/>
-      <c r="F32" s="199"/>
-      <c r="G32" s="199"/>
-      <c r="H32" s="194"/>
+      <c r="A32" s="177"/>
+      <c r="B32" s="177"/>
+      <c r="C32" s="232"/>
+      <c r="D32" s="175"/>
+      <c r="E32" s="175"/>
+      <c r="F32" s="175"/>
+      <c r="G32" s="175"/>
+      <c r="H32" s="176"/>
       <c r="I32" s="104" t="s">
         <v>67</v>
       </c>
@@ -10436,7 +10436,7 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="48" customHeight="1">
-      <c r="A33" s="207" t="s">
+      <c r="A33" s="177" t="s">
         <v>69</v>
       </c>
       <c r="B33" s="73" t="s">
@@ -10460,15 +10460,15 @@
       <c r="H33" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="I33" s="208" t="s">
+      <c r="I33" s="178" t="s">
         <v>104</v>
       </c>
-      <c r="J33" s="225" t="s">
+      <c r="J33" s="244" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A34" s="207"/>
+      <c r="A34" s="177"/>
       <c r="B34" s="73" t="s">
         <v>72</v>
       </c>
@@ -10490,14 +10490,14 @@
       <c r="H34" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="I34" s="208"/>
-      <c r="J34" s="226"/>
+      <c r="I34" s="178"/>
+      <c r="J34" s="245"/>
     </row>
     <row r="35" spans="1:10" ht="51" customHeight="1">
-      <c r="A35" s="200" t="s">
+      <c r="A35" s="186" t="s">
         <v>109</v>
       </c>
-      <c r="B35" s="200"/>
+      <c r="B35" s="186"/>
       <c r="C35" s="74"/>
       <c r="D35" s="91" t="s">
         <v>0</v>
@@ -10522,103 +10522,103 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="33" customHeight="1">
-      <c r="A36" s="204" t="s">
+      <c r="A36" s="264" t="s">
         <v>52</v>
       </c>
-      <c r="B36" s="201" t="s">
+      <c r="B36" s="280" t="s">
         <v>31</v>
       </c>
-      <c r="C36" s="202" t="s">
+      <c r="C36" s="197" t="s">
         <v>11</v>
       </c>
-      <c r="D36" s="199" t="s">
+      <c r="D36" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="E36" s="199" t="s">
+      <c r="E36" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="F36" s="199" t="s">
+      <c r="F36" s="175" t="s">
         <v>244</v>
       </c>
-      <c r="G36" s="199" t="s">
+      <c r="G36" s="175" t="s">
         <v>244</v>
       </c>
-      <c r="H36" s="199" t="s">
+      <c r="H36" s="175" t="s">
         <v>244</v>
       </c>
-      <c r="I36" s="203" t="s">
+      <c r="I36" s="263" t="s">
         <v>245</v>
       </c>
-      <c r="J36" s="193" t="s">
+      <c r="J36" s="181" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="60" customHeight="1">
-      <c r="A37" s="205"/>
-      <c r="B37" s="201"/>
-      <c r="C37" s="202"/>
-      <c r="D37" s="199"/>
-      <c r="E37" s="199"/>
-      <c r="F37" s="199"/>
-      <c r="G37" s="199"/>
-      <c r="H37" s="199"/>
-      <c r="I37" s="203"/>
-      <c r="J37" s="193"/>
+      <c r="A37" s="265"/>
+      <c r="B37" s="280"/>
+      <c r="C37" s="197"/>
+      <c r="D37" s="175"/>
+      <c r="E37" s="175"/>
+      <c r="F37" s="175"/>
+      <c r="G37" s="175"/>
+      <c r="H37" s="175"/>
+      <c r="I37" s="263"/>
+      <c r="J37" s="181"/>
     </row>
     <row r="38" spans="1:10" ht="346.5" customHeight="1">
-      <c r="A38" s="205"/>
+      <c r="A38" s="265"/>
       <c r="B38" s="154" t="s">
         <v>136</v>
       </c>
       <c r="C38" s="61"/>
-      <c r="D38" s="199"/>
-      <c r="E38" s="199"/>
-      <c r="F38" s="199"/>
-      <c r="G38" s="199"/>
-      <c r="H38" s="199"/>
-      <c r="I38" s="203"/>
+      <c r="D38" s="175"/>
+      <c r="E38" s="175"/>
+      <c r="F38" s="175"/>
+      <c r="G38" s="175"/>
+      <c r="H38" s="175"/>
+      <c r="I38" s="263"/>
       <c r="J38" s="45" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="111.75" customHeight="1">
-      <c r="A39" s="205"/>
+      <c r="A39" s="265"/>
       <c r="B39" s="154" t="s">
         <v>132</v>
       </c>
       <c r="C39" s="61"/>
-      <c r="D39" s="199"/>
-      <c r="E39" s="199"/>
-      <c r="F39" s="199"/>
-      <c r="G39" s="199"/>
-      <c r="H39" s="199"/>
-      <c r="I39" s="203"/>
+      <c r="D39" s="175"/>
+      <c r="E39" s="175"/>
+      <c r="F39" s="175"/>
+      <c r="G39" s="175"/>
+      <c r="H39" s="175"/>
+      <c r="I39" s="263"/>
       <c r="J39" s="76" t="s">
         <v>260</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="55.5" customHeight="1">
-      <c r="A40" s="205"/>
+      <c r="A40" s="265"/>
       <c r="B40" s="154" t="s">
         <v>13</v>
       </c>
       <c r="C40" s="61"/>
-      <c r="D40" s="199"/>
-      <c r="E40" s="199"/>
-      <c r="F40" s="199"/>
-      <c r="G40" s="199"/>
-      <c r="H40" s="199"/>
-      <c r="I40" s="203"/>
+      <c r="D40" s="175"/>
+      <c r="E40" s="175"/>
+      <c r="F40" s="175"/>
+      <c r="G40" s="175"/>
+      <c r="H40" s="175"/>
+      <c r="I40" s="263"/>
       <c r="J40" s="46" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="99" hidden="1" customHeight="1">
-      <c r="A41" s="205"/>
+      <c r="A41" s="265"/>
       <c r="B41" s="155" t="s">
         <v>157</v>
       </c>
-      <c r="C41" s="202" t="s">
+      <c r="C41" s="197" t="s">
         <v>159</v>
       </c>
       <c r="D41" s="91"/>
@@ -10634,11 +10634,11 @@
       </c>
     </row>
     <row r="42" spans="1:10" ht="93" hidden="1" customHeight="1">
-      <c r="A42" s="206"/>
+      <c r="A42" s="266"/>
       <c r="B42" s="155" t="s">
         <v>158</v>
       </c>
-      <c r="C42" s="202"/>
+      <c r="C42" s="197"/>
       <c r="D42" s="91"/>
       <c r="E42" s="91"/>
       <c r="F42" s="91"/>
@@ -10650,7 +10650,7 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="307.5" customHeight="1">
-      <c r="A43" s="201" t="s">
+      <c r="A43" s="280" t="s">
         <v>110</v>
       </c>
       <c r="B43" s="154" t="s">
@@ -10680,7 +10680,7 @@
       </c>
     </row>
     <row r="44" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A44" s="201"/>
+      <c r="A44" s="280"/>
       <c r="B44" s="154" t="s">
         <v>145</v>
       </c>
@@ -10708,7 +10708,7 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="141" customHeight="1">
-      <c r="A45" s="201"/>
+      <c r="A45" s="280"/>
       <c r="B45" s="154" t="s">
         <v>143</v>
       </c>
@@ -10718,7 +10718,7 @@
       <c r="F45" s="44"/>
       <c r="G45" s="44"/>
       <c r="H45" s="44"/>
-      <c r="I45" s="203" t="s">
+      <c r="I45" s="263" t="s">
         <v>246</v>
       </c>
       <c r="J45" s="47" t="s">
@@ -10726,7 +10726,7 @@
       </c>
     </row>
     <row r="46" spans="1:10" ht="18">
-      <c r="A46" s="201"/>
+      <c r="A46" s="280"/>
       <c r="B46" s="154" t="s">
         <v>144</v>
       </c>
@@ -10736,13 +10736,13 @@
       <c r="F46" s="44"/>
       <c r="G46" s="44"/>
       <c r="H46" s="44"/>
-      <c r="I46" s="203"/>
+      <c r="I46" s="263"/>
       <c r="J46" s="49" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="18">
-      <c r="A47" s="201"/>
+      <c r="A47" s="280"/>
       <c r="B47" s="154" t="s">
         <v>87</v>
       </c>
@@ -10752,13 +10752,13 @@
       <c r="F47" s="44"/>
       <c r="G47" s="44"/>
       <c r="H47" s="44"/>
-      <c r="I47" s="203"/>
+      <c r="I47" s="263"/>
       <c r="J47" s="49" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="18">
-      <c r="A48" s="201"/>
+      <c r="A48" s="280"/>
       <c r="B48" s="154" t="s">
         <v>88</v>
       </c>
@@ -10768,13 +10768,13 @@
       <c r="F48" s="44"/>
       <c r="G48" s="44"/>
       <c r="H48" s="44"/>
-      <c r="I48" s="203"/>
+      <c r="I48" s="263"/>
       <c r="J48" s="49" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="18">
-      <c r="A49" s="201"/>
+      <c r="A49" s="280"/>
       <c r="B49" s="154" t="s">
         <v>89</v>
       </c>
@@ -10784,13 +10784,13 @@
       <c r="F49" s="44"/>
       <c r="G49" s="44"/>
       <c r="H49" s="44"/>
-      <c r="I49" s="203"/>
+      <c r="I49" s="263"/>
       <c r="J49" s="49" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="18">
-      <c r="A50" s="201"/>
+      <c r="A50" s="280"/>
       <c r="B50" s="154" t="s">
         <v>90</v>
       </c>
@@ -10800,13 +10800,13 @@
       <c r="F50" s="44"/>
       <c r="G50" s="44"/>
       <c r="H50" s="44"/>
-      <c r="I50" s="203"/>
+      <c r="I50" s="263"/>
       <c r="J50" s="49" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="18">
-      <c r="A51" s="201"/>
+      <c r="A51" s="280"/>
       <c r="B51" s="154" t="s">
         <v>91</v>
       </c>
@@ -10816,13 +10816,13 @@
       <c r="F51" s="44"/>
       <c r="G51" s="44"/>
       <c r="H51" s="44"/>
-      <c r="I51" s="203"/>
+      <c r="I51" s="263"/>
       <c r="J51" s="49" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="18">
-      <c r="A52" s="201"/>
+      <c r="A52" s="280"/>
       <c r="B52" s="154" t="s">
         <v>92</v>
       </c>
@@ -10832,13 +10832,13 @@
       <c r="F52" s="44"/>
       <c r="G52" s="44"/>
       <c r="H52" s="44"/>
-      <c r="I52" s="203"/>
+      <c r="I52" s="263"/>
       <c r="J52" s="49" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="18">
-      <c r="A53" s="201"/>
+      <c r="A53" s="280"/>
       <c r="B53" s="154" t="s">
         <v>108</v>
       </c>
@@ -10848,13 +10848,13 @@
       <c r="F53" s="44"/>
       <c r="G53" s="44"/>
       <c r="H53" s="44"/>
-      <c r="I53" s="203"/>
+      <c r="I53" s="263"/>
       <c r="J53" s="49" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="104.25" customHeight="1">
-      <c r="A54" s="201"/>
+      <c r="A54" s="280"/>
       <c r="B54" s="154" t="s">
         <v>10</v>
       </c>
@@ -10864,13 +10864,13 @@
       <c r="F54" s="44"/>
       <c r="G54" s="44"/>
       <c r="H54" s="44"/>
-      <c r="I54" s="203"/>
+      <c r="I54" s="263"/>
       <c r="J54" s="50" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="99" customHeight="1">
-      <c r="A55" s="201"/>
+      <c r="A55" s="280"/>
       <c r="B55" s="154" t="s">
         <v>106</v>
       </c>
@@ -10880,13 +10880,13 @@
       <c r="F55" s="44"/>
       <c r="G55" s="44"/>
       <c r="H55" s="44"/>
-      <c r="I55" s="203"/>
+      <c r="I55" s="263"/>
       <c r="J55" s="51" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="69.75" customHeight="1">
-      <c r="A56" s="201"/>
+      <c r="A56" s="280"/>
       <c r="B56" s="154" t="s">
         <v>133</v>
       </c>
@@ -10896,13 +10896,13 @@
       <c r="F56" s="44"/>
       <c r="G56" s="44"/>
       <c r="H56" s="44"/>
-      <c r="I56" s="203"/>
+      <c r="I56" s="263"/>
       <c r="J56" s="49" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="70.5" customHeight="1">
-      <c r="A57" s="201"/>
+      <c r="A57" s="280"/>
       <c r="B57" s="154" t="s">
         <v>134</v>
       </c>
@@ -10912,13 +10912,13 @@
       <c r="F57" s="44"/>
       <c r="G57" s="44"/>
       <c r="H57" s="44"/>
-      <c r="I57" s="203"/>
+      <c r="I57" s="263"/>
       <c r="J57" s="49" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="53.25" customHeight="1">
-      <c r="A58" s="201"/>
+      <c r="A58" s="280"/>
       <c r="B58" s="156" t="s">
         <v>135</v>
       </c>
@@ -10940,13 +10940,13 @@
       <c r="H58" s="91" t="s">
         <v>244</v>
       </c>
-      <c r="I58" s="203"/>
+      <c r="I58" s="263"/>
       <c r="J58" s="49" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="95.25" customHeight="1">
-      <c r="A59" s="201"/>
+      <c r="A59" s="280"/>
       <c r="B59" s="156" t="s">
         <v>135</v>
       </c>
@@ -10968,13 +10968,13 @@
       <c r="H59" s="91" t="s">
         <v>247</v>
       </c>
-      <c r="I59" s="203"/>
+      <c r="I59" s="263"/>
       <c r="J59" s="52" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="89.25" customHeight="1">
-      <c r="A60" s="201"/>
+      <c r="A60" s="280"/>
       <c r="B60" s="154" t="s">
         <v>93</v>
       </c>
@@ -10984,13 +10984,13 @@
       <c r="F60" s="44"/>
       <c r="G60" s="44"/>
       <c r="H60" s="44"/>
-      <c r="I60" s="203"/>
+      <c r="I60" s="263"/>
       <c r="J60" s="49" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="72" customHeight="1">
-      <c r="A61" s="201"/>
+      <c r="A61" s="280"/>
       <c r="B61" s="154" t="s">
         <v>107</v>
       </c>
@@ -11000,13 +11000,13 @@
       <c r="F61" s="44"/>
       <c r="G61" s="44"/>
       <c r="H61" s="44"/>
-      <c r="I61" s="203"/>
+      <c r="I61" s="263"/>
       <c r="J61" s="49" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="53.25" customHeight="1">
-      <c r="A62" s="201"/>
+      <c r="A62" s="280"/>
       <c r="B62" s="154" t="s">
         <v>53</v>
       </c>
@@ -11016,13 +11016,13 @@
       <c r="F62" s="44"/>
       <c r="G62" s="44"/>
       <c r="H62" s="44"/>
-      <c r="I62" s="203"/>
+      <c r="I62" s="263"/>
       <c r="J62" s="47" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="48" customHeight="1">
-      <c r="A63" s="201"/>
+      <c r="A63" s="280"/>
       <c r="B63" s="154" t="s">
         <v>94</v>
       </c>
@@ -11048,10 +11048,10 @@
       </c>
     </row>
     <row r="64" spans="1:10" s="29" customFormat="1" ht="58.5" hidden="1" customHeight="1">
-      <c r="A64" s="200" t="s">
+      <c r="A64" s="186" t="s">
         <v>120</v>
       </c>
-      <c r="B64" s="200"/>
+      <c r="B64" s="186"/>
       <c r="C64" s="74" t="s">
         <v>123</v>
       </c>
@@ -11070,27 +11070,27 @@
       </c>
     </row>
     <row r="65" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A65" s="200" t="s">
+      <c r="A65" s="186" t="s">
         <v>28</v>
       </c>
-      <c r="B65" s="200"/>
-      <c r="C65" s="202"/>
-      <c r="D65" s="199" t="s">
+      <c r="B65" s="186"/>
+      <c r="C65" s="197"/>
+      <c r="D65" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="E65" s="199" t="s">
+      <c r="E65" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="F65" s="199" t="s">
+      <c r="F65" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="G65" s="199" t="s">
+      <c r="G65" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="H65" s="199" t="s">
+      <c r="H65" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="I65" s="210" t="s">
+      <c r="I65" s="215" t="s">
         <v>249</v>
       </c>
       <c r="J65" s="76" t="s">
@@ -11098,91 +11098,91 @@
       </c>
     </row>
     <row r="66" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A66" s="200"/>
-      <c r="B66" s="200"/>
-      <c r="C66" s="202"/>
-      <c r="D66" s="199"/>
-      <c r="E66" s="199"/>
-      <c r="F66" s="199"/>
-      <c r="G66" s="199"/>
-      <c r="H66" s="199"/>
-      <c r="I66" s="210"/>
+      <c r="A66" s="186"/>
+      <c r="B66" s="186"/>
+      <c r="C66" s="197"/>
+      <c r="D66" s="175"/>
+      <c r="E66" s="175"/>
+      <c r="F66" s="175"/>
+      <c r="G66" s="175"/>
+      <c r="H66" s="175"/>
+      <c r="I66" s="215"/>
       <c r="J66" s="55" t="s">
         <v>175</v>
       </c>
     </row>
     <row r="67" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A67" s="200"/>
-      <c r="B67" s="200"/>
-      <c r="C67" s="202"/>
-      <c r="D67" s="199"/>
-      <c r="E67" s="199"/>
-      <c r="F67" s="199"/>
-      <c r="G67" s="199"/>
-      <c r="H67" s="199"/>
-      <c r="I67" s="210"/>
+      <c r="A67" s="186"/>
+      <c r="B67" s="186"/>
+      <c r="C67" s="197"/>
+      <c r="D67" s="175"/>
+      <c r="E67" s="175"/>
+      <c r="F67" s="175"/>
+      <c r="G67" s="175"/>
+      <c r="H67" s="175"/>
+      <c r="I67" s="215"/>
       <c r="J67" s="76" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="68" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A68" s="200"/>
-      <c r="B68" s="200"/>
-      <c r="C68" s="202"/>
-      <c r="D68" s="199"/>
-      <c r="E68" s="199"/>
-      <c r="F68" s="199"/>
-      <c r="G68" s="199"/>
-      <c r="H68" s="199"/>
-      <c r="I68" s="210"/>
+      <c r="A68" s="186"/>
+      <c r="B68" s="186"/>
+      <c r="C68" s="197"/>
+      <c r="D68" s="175"/>
+      <c r="E68" s="175"/>
+      <c r="F68" s="175"/>
+      <c r="G68" s="175"/>
+      <c r="H68" s="175"/>
+      <c r="I68" s="215"/>
       <c r="J68" s="55" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="69" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A69" s="200"/>
-      <c r="B69" s="200"/>
-      <c r="C69" s="202"/>
-      <c r="D69" s="199"/>
-      <c r="E69" s="199"/>
-      <c r="F69" s="199"/>
-      <c r="G69" s="199"/>
-      <c r="H69" s="199"/>
-      <c r="I69" s="210"/>
+      <c r="A69" s="186"/>
+      <c r="B69" s="186"/>
+      <c r="C69" s="197"/>
+      <c r="D69" s="175"/>
+      <c r="E69" s="175"/>
+      <c r="F69" s="175"/>
+      <c r="G69" s="175"/>
+      <c r="H69" s="175"/>
+      <c r="I69" s="215"/>
       <c r="J69" s="76" t="s">
         <v>176</v>
       </c>
     </row>
     <row r="70" spans="1:11" ht="27.75" customHeight="1">
-      <c r="A70" s="200"/>
-      <c r="B70" s="200"/>
-      <c r="C70" s="202"/>
-      <c r="D70" s="199"/>
-      <c r="E70" s="199"/>
-      <c r="F70" s="199"/>
-      <c r="G70" s="199"/>
-      <c r="H70" s="199"/>
-      <c r="I70" s="210"/>
+      <c r="A70" s="186"/>
+      <c r="B70" s="186"/>
+      <c r="C70" s="197"/>
+      <c r="D70" s="175"/>
+      <c r="E70" s="175"/>
+      <c r="F70" s="175"/>
+      <c r="G70" s="175"/>
+      <c r="H70" s="175"/>
+      <c r="I70" s="215"/>
       <c r="J70" s="55" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="71" spans="1:11" ht="49.5" customHeight="1">
-      <c r="A71" s="200"/>
-      <c r="B71" s="200"/>
-      <c r="C71" s="202"/>
-      <c r="D71" s="199"/>
-      <c r="E71" s="199"/>
-      <c r="F71" s="199"/>
-      <c r="G71" s="199"/>
-      <c r="H71" s="199"/>
-      <c r="I71" s="210"/>
+      <c r="A71" s="186"/>
+      <c r="B71" s="186"/>
+      <c r="C71" s="197"/>
+      <c r="D71" s="175"/>
+      <c r="E71" s="175"/>
+      <c r="F71" s="175"/>
+      <c r="G71" s="175"/>
+      <c r="H71" s="175"/>
+      <c r="I71" s="215"/>
       <c r="J71" s="76" t="s">
         <v>272</v>
       </c>
     </row>
     <row r="72" spans="1:11" ht="100.5" hidden="1" customHeight="1">
-      <c r="A72" s="200" t="s">
+      <c r="A72" s="186" t="s">
         <v>74</v>
       </c>
       <c r="B72" s="78" t="s">
@@ -11214,7 +11214,7 @@
       </c>
     </row>
     <row r="73" spans="1:11" ht="61.5" customHeight="1">
-      <c r="A73" s="200"/>
+      <c r="A73" s="186"/>
       <c r="B73" s="78" t="s">
         <v>29</v>
       </c>
@@ -11242,10 +11242,10 @@
       </c>
     </row>
     <row r="74" spans="1:11" ht="96" customHeight="1">
-      <c r="A74" s="200" t="s">
+      <c r="A74" s="186" t="s">
         <v>46</v>
       </c>
-      <c r="B74" s="200"/>
+      <c r="B74" s="186"/>
       <c r="C74" s="74" t="s">
         <v>47</v>
       </c>
@@ -11290,13 +11290,13 @@
       </c>
     </row>
     <row r="77" spans="1:11" ht="65.25" customHeight="1">
-      <c r="A77" s="207" t="s">
+      <c r="A77" s="177" t="s">
         <v>59</v>
       </c>
       <c r="B77" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="C77" s="228" t="s">
+      <c r="C77" s="232" t="s">
         <v>78</v>
       </c>
       <c r="D77" s="91" t="s">
@@ -11322,24 +11322,24 @@
       </c>
     </row>
     <row r="78" spans="1:11" ht="90">
-      <c r="A78" s="207"/>
-      <c r="B78" s="207" t="s">
+      <c r="A78" s="177"/>
+      <c r="B78" s="177" t="s">
         <v>64</v>
       </c>
-      <c r="C78" s="228"/>
-      <c r="D78" s="199" t="s">
+      <c r="C78" s="232"/>
+      <c r="D78" s="175" t="s">
         <v>241</v>
       </c>
-      <c r="E78" s="199" t="s">
+      <c r="E78" s="175" t="s">
         <v>241</v>
       </c>
-      <c r="F78" s="199" t="s">
+      <c r="F78" s="175" t="s">
         <v>241</v>
       </c>
-      <c r="G78" s="199" t="s">
+      <c r="G78" s="175" t="s">
         <v>241</v>
       </c>
-      <c r="H78" s="194" t="s">
+      <c r="H78" s="176" t="s">
         <v>62</v>
       </c>
       <c r="I78" s="104" t="s">
@@ -11350,14 +11350,14 @@
       </c>
     </row>
     <row r="79" spans="1:11" ht="49.5" customHeight="1">
-      <c r="A79" s="207"/>
-      <c r="B79" s="207"/>
-      <c r="C79" s="228"/>
-      <c r="D79" s="199"/>
-      <c r="E79" s="199"/>
-      <c r="F79" s="199"/>
-      <c r="G79" s="199"/>
-      <c r="H79" s="194"/>
+      <c r="A79" s="177"/>
+      <c r="B79" s="177"/>
+      <c r="C79" s="232"/>
+      <c r="D79" s="175"/>
+      <c r="E79" s="175"/>
+      <c r="F79" s="175"/>
+      <c r="G79" s="175"/>
+      <c r="H79" s="176"/>
       <c r="I79" s="104" t="s">
         <v>67</v>
       </c>
@@ -11366,7 +11366,7 @@
       </c>
     </row>
     <row r="80" spans="1:11" ht="48" customHeight="1">
-      <c r="A80" s="207" t="s">
+      <c r="A80" s="177" t="s">
         <v>69</v>
       </c>
       <c r="B80" s="73" t="s">
@@ -11390,15 +11390,15 @@
       <c r="H80" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="I80" s="208" t="s">
+      <c r="I80" s="178" t="s">
         <v>104</v>
       </c>
-      <c r="J80" s="225" t="s">
+      <c r="J80" s="244" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="90" customHeight="1">
-      <c r="A81" s="207"/>
+      <c r="A81" s="177"/>
       <c r="B81" s="73" t="s">
         <v>72</v>
       </c>
@@ -11420,8 +11420,8 @@
       <c r="H81" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="I81" s="208"/>
-      <c r="J81" s="226"/>
+      <c r="I81" s="178"/>
+      <c r="J81" s="245"/>
     </row>
     <row r="83" spans="1:10">
       <c r="A83" s="12" t="s">
@@ -11431,35 +11431,35 @@
       <c r="C83" s="1"/>
     </row>
     <row r="84" spans="1:10" ht="42" customHeight="1">
-      <c r="A84" s="175" t="s">
+      <c r="A84" s="262" t="s">
         <v>22</v>
       </c>
-      <c r="B84" s="175"/>
-      <c r="C84" s="175" t="s">
+      <c r="B84" s="262"/>
+      <c r="C84" s="262" t="s">
         <v>6</v>
       </c>
-      <c r="D84" s="175" t="s">
+      <c r="D84" s="262" t="s">
         <v>7</v>
       </c>
-      <c r="E84" s="175"/>
-      <c r="F84" s="175" t="s">
+      <c r="E84" s="262"/>
+      <c r="F84" s="262" t="s">
         <v>8</v>
       </c>
-      <c r="G84" s="175"/>
-      <c r="H84" s="183" t="s">
+      <c r="G84" s="262"/>
+      <c r="H84" s="204" t="s">
         <v>9</v>
       </c>
-      <c r="I84" s="175" t="s">
+      <c r="I84" s="262" t="s">
         <v>2</v>
       </c>
-      <c r="J84" s="175" t="s">
+      <c r="J84" s="262" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="85" spans="1:10" ht="29.25" customHeight="1">
-      <c r="A85" s="175"/>
-      <c r="B85" s="175"/>
-      <c r="C85" s="175"/>
+      <c r="A85" s="262"/>
+      <c r="B85" s="262"/>
+      <c r="C85" s="262"/>
       <c r="D85" s="33" t="s">
         <v>3</v>
       </c>
@@ -11472,18 +11472,18 @@
       <c r="G85" s="33" t="s">
         <v>4</v>
       </c>
-      <c r="H85" s="183"/>
-      <c r="I85" s="175"/>
-      <c r="J85" s="175"/>
+      <c r="H85" s="204"/>
+      <c r="I85" s="262"/>
+      <c r="J85" s="262"/>
     </row>
     <row r="86" spans="1:10" ht="91.5" customHeight="1">
-      <c r="A86" s="176" t="s">
+      <c r="A86" s="267" t="s">
         <v>59</v>
       </c>
       <c r="B86" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="C86" s="179" t="s">
+      <c r="C86" s="220" t="s">
         <v>99</v>
       </c>
       <c r="D86" s="19" t="s">
@@ -11501,7 +11501,7 @@
       <c r="H86" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="I86" s="181" t="s">
+      <c r="I86" s="222" t="s">
         <v>100</v>
       </c>
       <c r="J86" s="18" t="s">
@@ -11509,11 +11509,11 @@
       </c>
     </row>
     <row r="87" spans="1:10" ht="124.5" customHeight="1">
-      <c r="A87" s="177"/>
+      <c r="A87" s="268"/>
       <c r="B87" s="35" t="s">
         <v>101</v>
       </c>
-      <c r="C87" s="180"/>
+      <c r="C87" s="221"/>
       <c r="D87" s="23" t="s">
         <v>5</v>
       </c>
@@ -11529,13 +11529,13 @@
       <c r="H87" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I87" s="182"/>
+      <c r="I87" s="223"/>
       <c r="J87" s="22" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="88" spans="1:10" ht="91.5" customHeight="1">
-      <c r="A88" s="178"/>
+      <c r="A88" s="269"/>
       <c r="B88" s="36" t="s">
         <v>114</v>
       </c>
@@ -11565,10 +11565,10 @@
       </c>
     </row>
     <row r="89" spans="1:10" ht="205.5" customHeight="1">
-      <c r="A89" s="209" t="s">
+      <c r="A89" s="261" t="s">
         <v>50</v>
       </c>
-      <c r="B89" s="209"/>
+      <c r="B89" s="261"/>
       <c r="C89" s="25"/>
       <c r="D89" s="24"/>
       <c r="E89" s="24"/>
@@ -11767,17 +11767,78 @@
     <filterColumn colId="0" showButton="0"/>
   </autoFilter>
   <mergeCells count="107">
-    <mergeCell ref="J33:J34"/>
-    <mergeCell ref="F31:F32"/>
-    <mergeCell ref="G31:G32"/>
-    <mergeCell ref="H31:H32"/>
-    <mergeCell ref="A33:A34"/>
-    <mergeCell ref="I33:I34"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="C30:C32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="D31:D32"/>
-    <mergeCell ref="E31:E32"/>
+    <mergeCell ref="J84:J85"/>
+    <mergeCell ref="A86:A88"/>
+    <mergeCell ref="C86:C87"/>
+    <mergeCell ref="I86:I87"/>
+    <mergeCell ref="H84:H85"/>
+    <mergeCell ref="I84:I85"/>
+    <mergeCell ref="I14:I15"/>
+    <mergeCell ref="A14:B16"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="F24:F26"/>
+    <mergeCell ref="G24:G26"/>
+    <mergeCell ref="H24:H26"/>
+    <mergeCell ref="A18:B20"/>
+    <mergeCell ref="A21:B21"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="G65:G71"/>
+    <mergeCell ref="A64:B64"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A43:A63"/>
+    <mergeCell ref="D36:D40"/>
+    <mergeCell ref="C36:C37"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="E36:E40"/>
+    <mergeCell ref="F36:F40"/>
+    <mergeCell ref="G36:G40"/>
+    <mergeCell ref="H65:H71"/>
+    <mergeCell ref="H36:H40"/>
+    <mergeCell ref="I45:I62"/>
+    <mergeCell ref="C41:C42"/>
+    <mergeCell ref="A36:A42"/>
+    <mergeCell ref="A80:A81"/>
+    <mergeCell ref="I80:I81"/>
+    <mergeCell ref="I36:I40"/>
+    <mergeCell ref="I65:I71"/>
+    <mergeCell ref="A89:B89"/>
+    <mergeCell ref="A84:B85"/>
+    <mergeCell ref="C84:C85"/>
+    <mergeCell ref="D84:E84"/>
+    <mergeCell ref="F84:G84"/>
+    <mergeCell ref="A72:A73"/>
+    <mergeCell ref="A74:B74"/>
+    <mergeCell ref="A65:B71"/>
+    <mergeCell ref="C65:C71"/>
+    <mergeCell ref="D65:D71"/>
+    <mergeCell ref="E65:E71"/>
+    <mergeCell ref="F65:F71"/>
+    <mergeCell ref="A10:B11"/>
+    <mergeCell ref="C10:C11"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="A7:B9"/>
+    <mergeCell ref="C7:C9"/>
+    <mergeCell ref="D7:D9"/>
+    <mergeCell ref="E7:E9"/>
+    <mergeCell ref="J80:J81"/>
+    <mergeCell ref="I24:I26"/>
+    <mergeCell ref="B27:B29"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="C77:C79"/>
+    <mergeCell ref="B78:B79"/>
+    <mergeCell ref="D78:D79"/>
+    <mergeCell ref="E78:E79"/>
+    <mergeCell ref="F78:F79"/>
+    <mergeCell ref="G78:G79"/>
+    <mergeCell ref="H78:H79"/>
+    <mergeCell ref="A24:A29"/>
+    <mergeCell ref="B24:B26"/>
+    <mergeCell ref="C24:C26"/>
+    <mergeCell ref="D24:D26"/>
+    <mergeCell ref="E24:E26"/>
     <mergeCell ref="A12:B13"/>
     <mergeCell ref="C14:C15"/>
     <mergeCell ref="C12:C13"/>
@@ -11802,78 +11863,17 @@
     <mergeCell ref="D5:E5"/>
     <mergeCell ref="F5:G5"/>
     <mergeCell ref="G12:G13"/>
-    <mergeCell ref="A10:B11"/>
-    <mergeCell ref="C10:C11"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="E10:E11"/>
-    <mergeCell ref="A7:B9"/>
-    <mergeCell ref="C7:C9"/>
-    <mergeCell ref="D7:D9"/>
-    <mergeCell ref="E7:E9"/>
-    <mergeCell ref="J80:J81"/>
-    <mergeCell ref="I24:I26"/>
-    <mergeCell ref="B27:B29"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="C77:C79"/>
-    <mergeCell ref="B78:B79"/>
-    <mergeCell ref="D78:D79"/>
-    <mergeCell ref="E78:E79"/>
-    <mergeCell ref="F78:F79"/>
-    <mergeCell ref="G78:G79"/>
-    <mergeCell ref="H78:H79"/>
-    <mergeCell ref="A24:A29"/>
-    <mergeCell ref="B24:B26"/>
-    <mergeCell ref="C24:C26"/>
-    <mergeCell ref="D24:D26"/>
-    <mergeCell ref="E24:E26"/>
-    <mergeCell ref="A89:B89"/>
-    <mergeCell ref="A84:B85"/>
-    <mergeCell ref="C84:C85"/>
-    <mergeCell ref="D84:E84"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="A72:A73"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A65:B71"/>
-    <mergeCell ref="C65:C71"/>
-    <mergeCell ref="D65:D71"/>
-    <mergeCell ref="E65:E71"/>
-    <mergeCell ref="F65:F71"/>
-    <mergeCell ref="E36:E40"/>
-    <mergeCell ref="F36:F40"/>
-    <mergeCell ref="G36:G40"/>
-    <mergeCell ref="H65:H71"/>
-    <mergeCell ref="H36:H40"/>
-    <mergeCell ref="I45:I62"/>
-    <mergeCell ref="C41:C42"/>
-    <mergeCell ref="A36:A42"/>
-    <mergeCell ref="A80:A81"/>
-    <mergeCell ref="I80:I81"/>
-    <mergeCell ref="I36:I40"/>
-    <mergeCell ref="I65:I71"/>
-    <mergeCell ref="J84:J85"/>
-    <mergeCell ref="A86:A88"/>
-    <mergeCell ref="C86:C87"/>
-    <mergeCell ref="I86:I87"/>
-    <mergeCell ref="H84:H85"/>
-    <mergeCell ref="I84:I85"/>
-    <mergeCell ref="I14:I15"/>
-    <mergeCell ref="A14:B16"/>
-    <mergeCell ref="A22:B23"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="F24:F26"/>
-    <mergeCell ref="G24:G26"/>
-    <mergeCell ref="H24:H26"/>
-    <mergeCell ref="A18:B20"/>
-    <mergeCell ref="A21:B21"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="G65:G71"/>
-    <mergeCell ref="A64:B64"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A43:A63"/>
-    <mergeCell ref="D36:D40"/>
-    <mergeCell ref="C36:C37"/>
-    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="J33:J34"/>
+    <mergeCell ref="F31:F32"/>
+    <mergeCell ref="G31:G32"/>
+    <mergeCell ref="H31:H32"/>
+    <mergeCell ref="A33:A34"/>
+    <mergeCell ref="I33:I34"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="C30:C32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="D31:D32"/>
+    <mergeCell ref="E31:E32"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -11911,30 +11911,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15">
-      <c r="A1" s="255" t="s">
+      <c r="A1" s="234" t="s">
         <v>251</v>
       </c>
-      <c r="B1" s="255"/>
-      <c r="C1" s="255"/>
-      <c r="D1" s="255"/>
-      <c r="E1" s="255"/>
-      <c r="F1" s="255"/>
-      <c r="G1" s="255"/>
-      <c r="H1" s="255"/>
-      <c r="I1" s="255"/>
-      <c r="J1" s="255"/>
+      <c r="B1" s="234"/>
+      <c r="C1" s="234"/>
+      <c r="D1" s="234"/>
+      <c r="E1" s="234"/>
+      <c r="F1" s="234"/>
+      <c r="G1" s="234"/>
+      <c r="H1" s="234"/>
+      <c r="I1" s="234"/>
+      <c r="J1" s="234"/>
     </row>
     <row r="2" spans="1:10" ht="15">
-      <c r="A2" s="255"/>
-      <c r="B2" s="255"/>
-      <c r="C2" s="255"/>
-      <c r="D2" s="255"/>
-      <c r="E2" s="255"/>
-      <c r="F2" s="255"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="255"/>
-      <c r="I2" s="255"/>
-      <c r="J2" s="255"/>
+      <c r="A2" s="234"/>
+      <c r="B2" s="234"/>
+      <c r="C2" s="234"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="234"/>
+      <c r="G2" s="234"/>
+      <c r="H2" s="234"/>
+      <c r="I2" s="234"/>
+      <c r="J2" s="234"/>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="32" t="s">
@@ -12002,35 +12002,35 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="25.5" customHeight="1">
-      <c r="A8" s="248" t="s">
+      <c r="A8" s="203" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="248"/>
-      <c r="C8" s="248" t="s">
+      <c r="B8" s="203"/>
+      <c r="C8" s="203" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="248" t="s">
+      <c r="D8" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="248"/>
-      <c r="F8" s="248" t="s">
+      <c r="E8" s="203"/>
+      <c r="F8" s="203" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="248"/>
-      <c r="H8" s="183" t="s">
+      <c r="G8" s="203"/>
+      <c r="H8" s="204" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="248" t="s">
+      <c r="I8" s="203" t="s">
         <v>2</v>
       </c>
-      <c r="J8" s="248" t="s">
+      <c r="J8" s="203" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="25.5" customHeight="1">
-      <c r="A9" s="248"/>
-      <c r="B9" s="248"/>
-      <c r="C9" s="248"/>
+      <c r="A9" s="203"/>
+      <c r="B9" s="203"/>
+      <c r="C9" s="203"/>
       <c r="D9" s="63" t="s">
         <v>3</v>
       </c>
@@ -12043,15 +12043,15 @@
       <c r="G9" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="183"/>
-      <c r="I9" s="248"/>
-      <c r="J9" s="248"/>
+      <c r="H9" s="204"/>
+      <c r="I9" s="203"/>
+      <c r="J9" s="203"/>
     </row>
     <row r="10" spans="1:10" ht="263.25" customHeight="1">
-      <c r="A10" s="262" t="s">
+      <c r="A10" s="281" t="s">
         <v>274</v>
       </c>
-      <c r="B10" s="262"/>
+      <c r="B10" s="281"/>
       <c r="C10" s="64" t="s">
         <v>81</v>
       </c>
@@ -12068,29 +12068,29 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="101.25" customHeight="1">
-      <c r="A11" s="243" t="s">
+      <c r="A11" s="195" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="243"/>
-      <c r="C11" s="202" t="s">
+      <c r="B11" s="195"/>
+      <c r="C11" s="197" t="s">
         <v>82</v>
       </c>
-      <c r="D11" s="244" t="s">
+      <c r="D11" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="244" t="s">
+      <c r="E11" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="244" t="s">
+      <c r="F11" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="244" t="s">
+      <c r="G11" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="244" t="s">
+      <c r="H11" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="I11" s="256" t="s">
+      <c r="I11" s="207" t="s">
         <v>39</v>
       </c>
       <c r="J11" s="124" t="s">
@@ -12098,53 +12098,53 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A12" s="243"/>
-      <c r="B12" s="243"/>
-      <c r="C12" s="202"/>
-      <c r="D12" s="244"/>
-      <c r="E12" s="244"/>
-      <c r="F12" s="244"/>
-      <c r="G12" s="244"/>
-      <c r="H12" s="244"/>
-      <c r="I12" s="257"/>
+      <c r="A12" s="195"/>
+      <c r="B12" s="195"/>
+      <c r="C12" s="197"/>
+      <c r="D12" s="225"/>
+      <c r="E12" s="225"/>
+      <c r="F12" s="225"/>
+      <c r="G12" s="225"/>
+      <c r="H12" s="225"/>
+      <c r="I12" s="208"/>
       <c r="J12" s="125" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="96.75" customHeight="1">
-      <c r="A13" s="243"/>
-      <c r="B13" s="243"/>
-      <c r="C13" s="202"/>
-      <c r="D13" s="244"/>
-      <c r="E13" s="244"/>
-      <c r="F13" s="244"/>
-      <c r="G13" s="244"/>
-      <c r="H13" s="244"/>
-      <c r="I13" s="257"/>
+      <c r="A13" s="195"/>
+      <c r="B13" s="195"/>
+      <c r="C13" s="197"/>
+      <c r="D13" s="225"/>
+      <c r="E13" s="225"/>
+      <c r="F13" s="225"/>
+      <c r="G13" s="225"/>
+      <c r="H13" s="225"/>
+      <c r="I13" s="208"/>
       <c r="J13" s="125" t="s">
         <v>279</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="54.75" customHeight="1">
-      <c r="A14" s="243"/>
-      <c r="B14" s="243"/>
-      <c r="C14" s="202"/>
-      <c r="D14" s="244"/>
-      <c r="E14" s="244"/>
-      <c r="F14" s="244"/>
-      <c r="G14" s="244"/>
-      <c r="H14" s="244"/>
-      <c r="I14" s="257"/>
+      <c r="A14" s="195"/>
+      <c r="B14" s="195"/>
+      <c r="C14" s="197"/>
+      <c r="D14" s="225"/>
+      <c r="E14" s="225"/>
+      <c r="F14" s="225"/>
+      <c r="G14" s="225"/>
+      <c r="H14" s="225"/>
+      <c r="I14" s="208"/>
       <c r="J14" s="126" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="126.75" customHeight="1">
-      <c r="A15" s="243" t="s">
+      <c r="A15" s="195" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="243"/>
-      <c r="C15" s="202" t="s">
+      <c r="B15" s="195"/>
+      <c r="C15" s="197" t="s">
         <v>82</v>
       </c>
       <c r="D15" s="127" t="s">
@@ -12162,30 +12162,30 @@
       <c r="H15" s="127" t="s">
         <v>5</v>
       </c>
-      <c r="I15" s="242" t="s">
+      <c r="I15" s="214" t="s">
         <v>281</v>
       </c>
-      <c r="J15" s="242" t="s">
+      <c r="J15" s="214" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="36" customHeight="1">
-      <c r="A16" s="243"/>
-      <c r="B16" s="243"/>
-      <c r="C16" s="202"/>
+      <c r="A16" s="195"/>
+      <c r="B16" s="195"/>
+      <c r="C16" s="197"/>
       <c r="D16" s="127"/>
       <c r="E16" s="127"/>
       <c r="F16" s="127"/>
       <c r="G16" s="127"/>
       <c r="H16" s="127"/>
-      <c r="I16" s="242"/>
-      <c r="J16" s="242"/>
+      <c r="I16" s="214"/>
+      <c r="J16" s="214"/>
     </row>
     <row r="17" spans="1:10" ht="184.5" customHeight="1">
-      <c r="A17" s="243" t="s">
+      <c r="A17" s="195" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="243"/>
+      <c r="B17" s="195"/>
       <c r="C17" s="74" t="s">
         <v>36</v>
       </c>
@@ -12202,10 +12202,10 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="239.25" customHeight="1">
-      <c r="A18" s="243" t="s">
+      <c r="A18" s="195" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="243"/>
+      <c r="B18" s="195"/>
       <c r="C18" s="74" t="s">
         <v>179</v>
       </c>
@@ -12222,10 +12222,10 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="256.5" customHeight="1">
-      <c r="A19" s="243" t="s">
+      <c r="A19" s="195" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="243"/>
+      <c r="B19" s="195"/>
       <c r="C19" s="74" t="s">
         <v>103</v>
       </c>
@@ -12242,26 +12242,26 @@
       </c>
     </row>
     <row r="20" spans="1:10" ht="60" customHeight="1">
-      <c r="A20" s="243" t="s">
+      <c r="A20" s="195" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="243"/>
-      <c r="C20" s="202" t="s">
+      <c r="B20" s="195"/>
+      <c r="C20" s="197" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="244" t="s">
+      <c r="D20" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="E20" s="244" t="s">
+      <c r="E20" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="F20" s="244" t="s">
+      <c r="F20" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="G20" s="244" t="s">
+      <c r="G20" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H20" s="247"/>
+      <c r="H20" s="284"/>
       <c r="I20" s="122" t="s">
         <v>43</v>
       </c>
@@ -12270,14 +12270,14 @@
       </c>
     </row>
     <row r="21" spans="1:10" ht="61.5" customHeight="1">
-      <c r="A21" s="243"/>
-      <c r="B21" s="243"/>
-      <c r="C21" s="202"/>
-      <c r="D21" s="244"/>
-      <c r="E21" s="244"/>
-      <c r="F21" s="244"/>
-      <c r="G21" s="244"/>
-      <c r="H21" s="247"/>
+      <c r="A21" s="195"/>
+      <c r="B21" s="195"/>
+      <c r="C21" s="197"/>
+      <c r="D21" s="225"/>
+      <c r="E21" s="225"/>
+      <c r="F21" s="225"/>
+      <c r="G21" s="225"/>
+      <c r="H21" s="284"/>
       <c r="I21" s="122" t="s">
         <v>44</v>
       </c>
@@ -12286,27 +12286,27 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A22" s="246" t="s">
+      <c r="A22" s="196" t="s">
         <v>21</v>
       </c>
-      <c r="B22" s="246"/>
-      <c r="C22" s="202" t="s">
+      <c r="B22" s="196"/>
+      <c r="C22" s="197" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="244" t="s">
+      <c r="D22" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="E22" s="244" t="s">
+      <c r="E22" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="F22" s="244" t="s">
+      <c r="F22" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="G22" s="244" t="s">
+      <c r="G22" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H22" s="244"/>
-      <c r="I22" s="245" t="s">
+      <c r="H22" s="225"/>
+      <c r="I22" s="235" t="s">
         <v>284</v>
       </c>
       <c r="J22" s="56" t="s">
@@ -12314,25 +12314,25 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="18">
-      <c r="A23" s="246"/>
-      <c r="B23" s="246"/>
-      <c r="C23" s="202"/>
-      <c r="D23" s="244"/>
-      <c r="E23" s="244"/>
-      <c r="F23" s="244"/>
-      <c r="G23" s="244"/>
-      <c r="H23" s="244"/>
-      <c r="I23" s="245"/>
+      <c r="A23" s="196"/>
+      <c r="B23" s="196"/>
+      <c r="C23" s="197"/>
+      <c r="D23" s="225"/>
+      <c r="E23" s="225"/>
+      <c r="F23" s="225"/>
+      <c r="G23" s="225"/>
+      <c r="H23" s="225"/>
+      <c r="I23" s="235"/>
       <c r="J23" s="40" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:10" ht="57" customHeight="1">
-      <c r="A24" s="260" t="s">
+      <c r="A24" s="189" t="s">
         <v>217</v>
       </c>
-      <c r="B24" s="212"/>
-      <c r="C24" s="221" t="s">
+      <c r="B24" s="190"/>
+      <c r="C24" s="246" t="s">
         <v>224</v>
       </c>
       <c r="D24" s="89"/>
@@ -12340,7 +12340,7 @@
       <c r="F24" s="89"/>
       <c r="G24" s="89"/>
       <c r="H24" s="89"/>
-      <c r="I24" s="184" t="s">
+      <c r="I24" s="201" t="s">
         <v>222</v>
       </c>
       <c r="J24" s="163" t="s">
@@ -12348,22 +12348,22 @@
       </c>
     </row>
     <row r="25" spans="1:10" ht="102.75" customHeight="1">
-      <c r="A25" s="261"/>
-      <c r="B25" s="220"/>
-      <c r="C25" s="223"/>
+      <c r="A25" s="191"/>
+      <c r="B25" s="192"/>
+      <c r="C25" s="247"/>
       <c r="D25" s="89"/>
       <c r="E25" s="89"/>
       <c r="F25" s="89"/>
       <c r="G25" s="89"/>
       <c r="H25" s="89"/>
-      <c r="I25" s="185"/>
+      <c r="I25" s="202"/>
       <c r="J25" s="164" t="s">
         <v>230</v>
       </c>
     </row>
     <row r="26" spans="1:10" ht="114" customHeight="1">
-      <c r="A26" s="263"/>
-      <c r="B26" s="214"/>
+      <c r="A26" s="282"/>
+      <c r="B26" s="229"/>
       <c r="C26" s="159" t="s">
         <v>225</v>
       </c>
@@ -12378,10 +12378,10 @@
       </c>
     </row>
     <row r="27" spans="1:10" ht="57.75" customHeight="1">
-      <c r="A27" s="258" t="s">
+      <c r="A27" s="187" t="s">
         <v>285</v>
       </c>
-      <c r="B27" s="259"/>
+      <c r="B27" s="188"/>
       <c r="C27" s="160" t="s">
         <v>203</v>
       </c>
@@ -12396,10 +12396,10 @@
       </c>
     </row>
     <row r="28" spans="1:10" ht="87" customHeight="1">
-      <c r="A28" s="260" t="s">
+      <c r="A28" s="189" t="s">
         <v>233</v>
       </c>
-      <c r="B28" s="212"/>
+      <c r="B28" s="190"/>
       <c r="C28" s="158" t="s">
         <v>204</v>
       </c>
@@ -12414,8 +12414,8 @@
       </c>
     </row>
     <row r="29" spans="1:10" ht="162.75" customHeight="1">
-      <c r="A29" s="261"/>
-      <c r="B29" s="220"/>
+      <c r="A29" s="191"/>
+      <c r="B29" s="192"/>
       <c r="C29" s="158" t="s">
         <v>205</v>
       </c>
@@ -12432,8 +12432,8 @@
       </c>
     </row>
     <row r="30" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A30" s="261"/>
-      <c r="B30" s="220"/>
+      <c r="A30" s="191"/>
+      <c r="B30" s="192"/>
       <c r="C30" s="158"/>
       <c r="D30" s="93"/>
       <c r="E30" s="93"/>
@@ -12446,10 +12446,10 @@
       </c>
     </row>
     <row r="31" spans="1:10" ht="45.75" customHeight="1" thickBot="1">
-      <c r="A31" s="264" t="s">
+      <c r="A31" s="193" t="s">
         <v>237</v>
       </c>
-      <c r="B31" s="265"/>
+      <c r="B31" s="194"/>
       <c r="C31" s="161" t="s">
         <v>206</v>
       </c>
@@ -12464,11 +12464,11 @@
       </c>
     </row>
     <row r="32" spans="1:10" ht="108.75" customHeight="1" thickTop="1">
-      <c r="A32" s="246" t="s">
+      <c r="A32" s="196" t="s">
         <v>16</v>
       </c>
-      <c r="B32" s="246"/>
-      <c r="C32" s="202"/>
+      <c r="B32" s="196"/>
+      <c r="C32" s="197"/>
       <c r="D32" s="113"/>
       <c r="E32" s="91" t="s">
         <v>5</v>
@@ -12476,7 +12476,7 @@
       <c r="F32" s="113"/>
       <c r="G32" s="113"/>
       <c r="H32" s="113"/>
-      <c r="I32" s="193" t="s">
+      <c r="I32" s="181" t="s">
         <v>252</v>
       </c>
       <c r="J32" s="57" t="s">
@@ -12484,37 +12484,37 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="84" customHeight="1">
-      <c r="A33" s="246"/>
-      <c r="B33" s="246"/>
-      <c r="C33" s="202"/>
+      <c r="A33" s="196"/>
+      <c r="B33" s="196"/>
+      <c r="C33" s="197"/>
       <c r="D33" s="113"/>
       <c r="E33" s="91"/>
       <c r="F33" s="113"/>
       <c r="G33" s="113"/>
       <c r="H33" s="113"/>
-      <c r="I33" s="193"/>
+      <c r="I33" s="181"/>
       <c r="J33" s="40" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="51.75" customHeight="1">
-      <c r="A34" s="243" t="s">
+      <c r="A34" s="195" t="s">
         <v>286</v>
       </c>
-      <c r="B34" s="246" t="s">
+      <c r="B34" s="196" t="s">
         <v>287</v>
       </c>
-      <c r="C34" s="202" t="s">
+      <c r="C34" s="197" t="s">
         <v>26</v>
       </c>
-      <c r="D34" s="199" t="s">
+      <c r="D34" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="E34" s="200"/>
-      <c r="F34" s="200"/>
-      <c r="G34" s="200"/>
-      <c r="H34" s="200"/>
-      <c r="I34" s="208" t="s">
+      <c r="E34" s="186"/>
+      <c r="F34" s="186"/>
+      <c r="G34" s="186"/>
+      <c r="H34" s="186"/>
+      <c r="I34" s="178" t="s">
         <v>253</v>
       </c>
       <c r="J34" s="58" t="s">
@@ -12522,36 +12522,36 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="18">
-      <c r="A35" s="243"/>
-      <c r="B35" s="246"/>
-      <c r="C35" s="202"/>
-      <c r="D35" s="199"/>
-      <c r="E35" s="200"/>
-      <c r="F35" s="200"/>
-      <c r="G35" s="200"/>
-      <c r="H35" s="200"/>
-      <c r="I35" s="208"/>
+      <c r="A35" s="195"/>
+      <c r="B35" s="196"/>
+      <c r="C35" s="197"/>
+      <c r="D35" s="175"/>
+      <c r="E35" s="186"/>
+      <c r="F35" s="186"/>
+      <c r="G35" s="186"/>
+      <c r="H35" s="186"/>
+      <c r="I35" s="178"/>
       <c r="J35" s="42" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="36" spans="1:10" ht="45.75" customHeight="1">
-      <c r="A36" s="243"/>
-      <c r="B36" s="246"/>
-      <c r="C36" s="202"/>
-      <c r="D36" s="199"/>
-      <c r="E36" s="200"/>
-      <c r="F36" s="200"/>
-      <c r="G36" s="200"/>
-      <c r="H36" s="200"/>
-      <c r="I36" s="208"/>
+      <c r="A36" s="195"/>
+      <c r="B36" s="196"/>
+      <c r="C36" s="197"/>
+      <c r="D36" s="175"/>
+      <c r="E36" s="186"/>
+      <c r="F36" s="186"/>
+      <c r="G36" s="186"/>
+      <c r="H36" s="186"/>
+      <c r="I36" s="178"/>
       <c r="J36" s="58" t="s">
         <v>184</v>
       </c>
     </row>
     <row r="37" spans="1:10" ht="126" customHeight="1">
-      <c r="A37" s="243"/>
-      <c r="B37" s="254" t="s">
+      <c r="A37" s="195"/>
+      <c r="B37" s="198" t="s">
         <v>19</v>
       </c>
       <c r="C37" s="74" t="s">
@@ -12566,7 +12566,7 @@
       </c>
       <c r="G37" s="113"/>
       <c r="H37" s="113"/>
-      <c r="I37" s="208" t="s">
+      <c r="I37" s="178" t="s">
         <v>254</v>
       </c>
       <c r="J37" s="59" t="s">
@@ -12574,8 +12574,8 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="78.75" customHeight="1">
-      <c r="A38" s="243"/>
-      <c r="B38" s="254"/>
+      <c r="A38" s="195"/>
+      <c r="B38" s="198"/>
       <c r="C38" s="74" t="s">
         <v>156</v>
       </c>
@@ -12584,14 +12584,14 @@
       <c r="F38" s="91"/>
       <c r="G38" s="113"/>
       <c r="H38" s="113"/>
-      <c r="I38" s="208"/>
+      <c r="I38" s="178"/>
       <c r="J38" s="43" t="s">
         <v>164</v>
       </c>
     </row>
     <row r="39" spans="1:10" ht="42.75" customHeight="1">
-      <c r="A39" s="243"/>
-      <c r="B39" s="254"/>
+      <c r="A39" s="195"/>
+      <c r="B39" s="198"/>
       <c r="C39" s="74" t="s">
         <v>26</v>
       </c>
@@ -12604,33 +12604,33 @@
       </c>
       <c r="G39" s="113"/>
       <c r="H39" s="113"/>
-      <c r="I39" s="208"/>
+      <c r="I39" s="178"/>
       <c r="J39" s="66" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="40" spans="1:10" ht="37.5" customHeight="1">
-      <c r="A40" s="246" t="s">
+      <c r="A40" s="196" t="s">
         <v>14</v>
       </c>
-      <c r="B40" s="246"/>
-      <c r="C40" s="202"/>
-      <c r="D40" s="199" t="s">
+      <c r="B40" s="196"/>
+      <c r="C40" s="197"/>
+      <c r="D40" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="E40" s="199" t="s">
+      <c r="E40" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="F40" s="199" t="s">
+      <c r="F40" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="G40" s="199" t="s">
+      <c r="G40" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="H40" s="199" t="s">
+      <c r="H40" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="I40" s="210" t="s">
+      <c r="I40" s="215" t="s">
         <v>140</v>
       </c>
       <c r="J40" s="56" t="s">
@@ -12638,21 +12638,21 @@
       </c>
     </row>
     <row r="41" spans="1:10" ht="27" customHeight="1">
-      <c r="A41" s="246"/>
-      <c r="B41" s="246"/>
-      <c r="C41" s="202"/>
-      <c r="D41" s="199"/>
-      <c r="E41" s="199"/>
-      <c r="F41" s="199"/>
-      <c r="G41" s="199"/>
-      <c r="H41" s="199"/>
-      <c r="I41" s="210"/>
+      <c r="A41" s="196"/>
+      <c r="B41" s="196"/>
+      <c r="C41" s="197"/>
+      <c r="D41" s="175"/>
+      <c r="E41" s="175"/>
+      <c r="F41" s="175"/>
+      <c r="G41" s="175"/>
+      <c r="H41" s="175"/>
+      <c r="I41" s="215"/>
       <c r="J41" s="42" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="42" spans="1:10" ht="94.5" customHeight="1">
-      <c r="A42" s="253" t="s">
+      <c r="A42" s="200" t="s">
         <v>84</v>
       </c>
       <c r="B42" s="79" t="s">
@@ -12661,22 +12661,22 @@
       <c r="C42" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D42" s="199" t="s">
+      <c r="D42" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="E42" s="199" t="s">
+      <c r="E42" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="F42" s="199" t="s">
+      <c r="F42" s="175" t="s">
         <v>244</v>
       </c>
-      <c r="G42" s="199" t="s">
+      <c r="G42" s="175" t="s">
         <v>244</v>
       </c>
-      <c r="H42" s="199" t="s">
+      <c r="H42" s="175" t="s">
         <v>244</v>
       </c>
-      <c r="I42" s="252" t="s">
+      <c r="I42" s="199" t="s">
         <v>255</v>
       </c>
       <c r="J42" s="76" t="s">
@@ -12684,55 +12684,55 @@
       </c>
     </row>
     <row r="43" spans="1:10" ht="345" customHeight="1">
-      <c r="A43" s="253"/>
+      <c r="A43" s="200"/>
       <c r="B43" s="79" t="s">
         <v>12</v>
       </c>
       <c r="C43" s="74"/>
-      <c r="D43" s="199"/>
-      <c r="E43" s="199"/>
-      <c r="F43" s="199"/>
-      <c r="G43" s="199"/>
-      <c r="H43" s="199"/>
-      <c r="I43" s="252"/>
+      <c r="D43" s="175"/>
+      <c r="E43" s="175"/>
+      <c r="F43" s="175"/>
+      <c r="G43" s="175"/>
+      <c r="H43" s="175"/>
+      <c r="I43" s="199"/>
       <c r="J43" s="45" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="80.25" customHeight="1">
-      <c r="A44" s="253"/>
+      <c r="A44" s="200"/>
       <c r="B44" s="79" t="s">
         <v>139</v>
       </c>
       <c r="C44" s="74"/>
-      <c r="D44" s="199"/>
-      <c r="E44" s="199"/>
-      <c r="F44" s="199"/>
-      <c r="G44" s="199"/>
-      <c r="H44" s="199"/>
-      <c r="I44" s="252"/>
+      <c r="D44" s="175"/>
+      <c r="E44" s="175"/>
+      <c r="F44" s="175"/>
+      <c r="G44" s="175"/>
+      <c r="H44" s="175"/>
+      <c r="I44" s="199"/>
       <c r="J44" s="76" t="s">
         <v>267</v>
       </c>
     </row>
     <row r="45" spans="1:10" ht="52.5" customHeight="1">
-      <c r="A45" s="253"/>
+      <c r="A45" s="200"/>
       <c r="B45" s="79" t="s">
         <v>13</v>
       </c>
       <c r="C45" s="74"/>
-      <c r="D45" s="199"/>
-      <c r="E45" s="199"/>
-      <c r="F45" s="199"/>
-      <c r="G45" s="199"/>
-      <c r="H45" s="199"/>
-      <c r="I45" s="252"/>
+      <c r="D45" s="175"/>
+      <c r="E45" s="175"/>
+      <c r="F45" s="175"/>
+      <c r="G45" s="175"/>
+      <c r="H45" s="175"/>
+      <c r="I45" s="199"/>
       <c r="J45" s="49" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="339" customHeight="1">
-      <c r="A46" s="253" t="s">
+      <c r="A46" s="200" t="s">
         <v>161</v>
       </c>
       <c r="B46" s="79" t="s">
@@ -12754,13 +12754,13 @@
       <c r="H46" s="44" t="s">
         <v>244</v>
       </c>
-      <c r="I46" s="252"/>
+      <c r="I46" s="199"/>
       <c r="J46" s="48" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="66.75" customHeight="1">
-      <c r="A47" s="253"/>
+      <c r="A47" s="200"/>
       <c r="B47" s="75" t="s">
         <v>145</v>
       </c>
@@ -12782,13 +12782,13 @@
       <c r="H47" s="44" t="s">
         <v>244</v>
       </c>
-      <c r="I47" s="252"/>
+      <c r="I47" s="199"/>
       <c r="J47" s="60" t="s">
         <v>288</v>
       </c>
     </row>
     <row r="48" spans="1:10" ht="108">
-      <c r="A48" s="253"/>
+      <c r="A48" s="200"/>
       <c r="B48" s="79" t="s">
         <v>105</v>
       </c>
@@ -12798,13 +12798,13 @@
       <c r="F48" s="44"/>
       <c r="G48" s="44"/>
       <c r="H48" s="44"/>
-      <c r="I48" s="252"/>
+      <c r="I48" s="199"/>
       <c r="J48" s="47" t="s">
         <v>191</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="18">
-      <c r="A49" s="253"/>
+      <c r="A49" s="200"/>
       <c r="B49" s="79" t="s">
         <v>86</v>
       </c>
@@ -12814,13 +12814,13 @@
       <c r="F49" s="44"/>
       <c r="G49" s="44"/>
       <c r="H49" s="44"/>
-      <c r="I49" s="252"/>
+      <c r="I49" s="199"/>
       <c r="J49" s="49" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="50" spans="1:10" ht="18">
-      <c r="A50" s="253"/>
+      <c r="A50" s="200"/>
       <c r="B50" s="79" t="s">
         <v>87</v>
       </c>
@@ -12830,13 +12830,13 @@
       <c r="F50" s="44"/>
       <c r="G50" s="44"/>
       <c r="H50" s="44"/>
-      <c r="I50" s="252"/>
+      <c r="I50" s="199"/>
       <c r="J50" s="49" t="s">
         <v>192</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="18">
-      <c r="A51" s="253"/>
+      <c r="A51" s="200"/>
       <c r="B51" s="79" t="s">
         <v>88</v>
       </c>
@@ -12846,13 +12846,13 @@
       <c r="F51" s="44"/>
       <c r="G51" s="44"/>
       <c r="H51" s="44"/>
-      <c r="I51" s="252"/>
+      <c r="I51" s="199"/>
       <c r="J51" s="49" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="18">
-      <c r="A52" s="253"/>
+      <c r="A52" s="200"/>
       <c r="B52" s="79" t="s">
         <v>89</v>
       </c>
@@ -12862,13 +12862,13 @@
       <c r="F52" s="44"/>
       <c r="G52" s="44"/>
       <c r="H52" s="44"/>
-      <c r="I52" s="252"/>
+      <c r="I52" s="199"/>
       <c r="J52" s="49" t="s">
         <v>194</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="18">
-      <c r="A53" s="253"/>
+      <c r="A53" s="200"/>
       <c r="B53" s="79" t="s">
         <v>90</v>
       </c>
@@ -12878,13 +12878,13 @@
       <c r="F53" s="44"/>
       <c r="G53" s="44"/>
       <c r="H53" s="44"/>
-      <c r="I53" s="252"/>
+      <c r="I53" s="199"/>
       <c r="J53" s="49" t="s">
         <v>195</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="21" customHeight="1">
-      <c r="A54" s="253"/>
+      <c r="A54" s="200"/>
       <c r="B54" s="79" t="s">
         <v>91</v>
       </c>
@@ -12894,13 +12894,13 @@
       <c r="F54" s="44"/>
       <c r="G54" s="44"/>
       <c r="H54" s="44"/>
-      <c r="I54" s="252"/>
+      <c r="I54" s="199"/>
       <c r="J54" s="49" t="s">
         <v>196</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="21" customHeight="1">
-      <c r="A55" s="253"/>
+      <c r="A55" s="200"/>
       <c r="B55" s="79" t="s">
         <v>92</v>
       </c>
@@ -12910,13 +12910,13 @@
       <c r="F55" s="44"/>
       <c r="G55" s="44"/>
       <c r="H55" s="44"/>
-      <c r="I55" s="252"/>
+      <c r="I55" s="199"/>
       <c r="J55" s="49" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="18">
-      <c r="A56" s="253"/>
+      <c r="A56" s="200"/>
       <c r="B56" s="79" t="s">
         <v>108</v>
       </c>
@@ -12926,13 +12926,13 @@
       <c r="F56" s="44"/>
       <c r="G56" s="44"/>
       <c r="H56" s="44"/>
-      <c r="I56" s="252"/>
+      <c r="I56" s="199"/>
       <c r="J56" s="49" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="68.25" customHeight="1">
-      <c r="A57" s="253"/>
+      <c r="A57" s="200"/>
       <c r="B57" s="75" t="s">
         <v>10</v>
       </c>
@@ -12942,13 +12942,13 @@
       <c r="F57" s="44"/>
       <c r="G57" s="44"/>
       <c r="H57" s="44"/>
-      <c r="I57" s="252"/>
+      <c r="I57" s="199"/>
       <c r="J57" s="50" t="s">
         <v>262</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="66" customHeight="1">
-      <c r="A58" s="253"/>
+      <c r="A58" s="200"/>
       <c r="B58" s="75" t="s">
         <v>106</v>
       </c>
@@ -12958,13 +12958,13 @@
       <c r="F58" s="44"/>
       <c r="G58" s="44"/>
       <c r="H58" s="44"/>
-      <c r="I58" s="252"/>
+      <c r="I58" s="199"/>
       <c r="J58" s="51" t="s">
         <v>263</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A59" s="253"/>
+      <c r="A59" s="200"/>
       <c r="B59" s="75" t="s">
         <v>133</v>
       </c>
@@ -12974,13 +12974,13 @@
       <c r="F59" s="44"/>
       <c r="G59" s="44"/>
       <c r="H59" s="44"/>
-      <c r="I59" s="252"/>
+      <c r="I59" s="199"/>
       <c r="J59" s="49" t="s">
         <v>264</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A60" s="253"/>
+      <c r="A60" s="200"/>
       <c r="B60" s="75" t="s">
         <v>134</v>
       </c>
@@ -12990,13 +12990,13 @@
       <c r="F60" s="44"/>
       <c r="G60" s="44"/>
       <c r="H60" s="44"/>
-      <c r="I60" s="252"/>
+      <c r="I60" s="199"/>
       <c r="J60" s="49" t="s">
         <v>168</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A61" s="253"/>
+      <c r="A61" s="200"/>
       <c r="B61" s="75" t="s">
         <v>135</v>
       </c>
@@ -13008,13 +13008,13 @@
       <c r="F61" s="44"/>
       <c r="G61" s="44"/>
       <c r="H61" s="44"/>
-      <c r="I61" s="252"/>
+      <c r="I61" s="199"/>
       <c r="J61" s="49" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="60" customHeight="1">
-      <c r="A62" s="253"/>
+      <c r="A62" s="200"/>
       <c r="B62" s="75" t="s">
         <v>93</v>
       </c>
@@ -13024,13 +13024,13 @@
       <c r="F62" s="44"/>
       <c r="G62" s="44"/>
       <c r="H62" s="44"/>
-      <c r="I62" s="252"/>
+      <c r="I62" s="199"/>
       <c r="J62" s="49" t="s">
         <v>169</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A63" s="253"/>
+      <c r="A63" s="200"/>
       <c r="B63" s="75" t="s">
         <v>107</v>
       </c>
@@ -13040,13 +13040,13 @@
       <c r="F63" s="44"/>
       <c r="G63" s="44"/>
       <c r="H63" s="44"/>
-      <c r="I63" s="252"/>
+      <c r="I63" s="199"/>
       <c r="J63" s="49" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A64" s="253"/>
+      <c r="A64" s="200"/>
       <c r="B64" s="75" t="s">
         <v>53</v>
       </c>
@@ -13056,13 +13056,13 @@
       <c r="F64" s="44"/>
       <c r="G64" s="44"/>
       <c r="H64" s="44"/>
-      <c r="I64" s="252"/>
+      <c r="I64" s="199"/>
       <c r="J64" s="47" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="48" customHeight="1">
-      <c r="A65" s="253"/>
+      <c r="A65" s="200"/>
       <c r="B65" s="75" t="s">
         <v>94</v>
       </c>
@@ -13082,33 +13082,33 @@
       <c r="H65" s="91" t="s">
         <v>244</v>
       </c>
-      <c r="I65" s="252"/>
+      <c r="I65" s="199"/>
       <c r="J65" s="47" t="s">
         <v>174</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="24" customHeight="1">
-      <c r="A66" s="246" t="s">
+      <c r="A66" s="196" t="s">
         <v>28</v>
       </c>
-      <c r="B66" s="246"/>
-      <c r="C66" s="251"/>
-      <c r="D66" s="199" t="s">
+      <c r="B66" s="196"/>
+      <c r="C66" s="283"/>
+      <c r="D66" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="E66" s="199" t="s">
+      <c r="E66" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="F66" s="199" t="s">
+      <c r="F66" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="G66" s="199" t="s">
+      <c r="G66" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="H66" s="199" t="s">
+      <c r="H66" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="I66" s="210" t="s">
+      <c r="I66" s="215" t="s">
         <v>256</v>
       </c>
       <c r="J66" s="76" t="s">
@@ -13116,128 +13116,128 @@
       </c>
     </row>
     <row r="67" spans="1:10" ht="18">
-      <c r="A67" s="246"/>
-      <c r="B67" s="246"/>
-      <c r="C67" s="251"/>
-      <c r="D67" s="199"/>
-      <c r="E67" s="199"/>
-      <c r="F67" s="199"/>
-      <c r="G67" s="199"/>
-      <c r="H67" s="199"/>
-      <c r="I67" s="210"/>
+      <c r="A67" s="196"/>
+      <c r="B67" s="196"/>
+      <c r="C67" s="283"/>
+      <c r="D67" s="175"/>
+      <c r="E67" s="175"/>
+      <c r="F67" s="175"/>
+      <c r="G67" s="175"/>
+      <c r="H67" s="175"/>
+      <c r="I67" s="215"/>
       <c r="J67" s="55" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="21.75" customHeight="1">
-      <c r="A68" s="246"/>
-      <c r="B68" s="246"/>
-      <c r="C68" s="251"/>
-      <c r="D68" s="199"/>
-      <c r="E68" s="199"/>
-      <c r="F68" s="199"/>
-      <c r="G68" s="199"/>
-      <c r="H68" s="199"/>
-      <c r="I68" s="210"/>
+      <c r="A68" s="196"/>
+      <c r="B68" s="196"/>
+      <c r="C68" s="283"/>
+      <c r="D68" s="175"/>
+      <c r="E68" s="175"/>
+      <c r="F68" s="175"/>
+      <c r="G68" s="175"/>
+      <c r="H68" s="175"/>
+      <c r="I68" s="215"/>
       <c r="J68" s="76" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="18">
-      <c r="A69" s="246"/>
-      <c r="B69" s="246"/>
-      <c r="C69" s="251"/>
-      <c r="D69" s="199"/>
-      <c r="E69" s="199"/>
-      <c r="F69" s="199"/>
-      <c r="G69" s="199"/>
-      <c r="H69" s="199"/>
-      <c r="I69" s="210"/>
+      <c r="A69" s="196"/>
+      <c r="B69" s="196"/>
+      <c r="C69" s="283"/>
+      <c r="D69" s="175"/>
+      <c r="E69" s="175"/>
+      <c r="F69" s="175"/>
+      <c r="G69" s="175"/>
+      <c r="H69" s="175"/>
+      <c r="I69" s="215"/>
       <c r="J69" s="55" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="32.25" customHeight="1">
-      <c r="A70" s="246"/>
-      <c r="B70" s="246"/>
+      <c r="A70" s="196"/>
+      <c r="B70" s="196"/>
       <c r="C70" s="80" t="s">
         <v>128</v>
       </c>
-      <c r="D70" s="199"/>
-      <c r="E70" s="199"/>
-      <c r="F70" s="199"/>
-      <c r="G70" s="199"/>
-      <c r="H70" s="199"/>
-      <c r="I70" s="210"/>
+      <c r="D70" s="175"/>
+      <c r="E70" s="175"/>
+      <c r="F70" s="175"/>
+      <c r="G70" s="175"/>
+      <c r="H70" s="175"/>
+      <c r="I70" s="215"/>
       <c r="J70" s="67" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="18">
-      <c r="A71" s="246"/>
-      <c r="B71" s="246"/>
+      <c r="A71" s="196"/>
+      <c r="B71" s="196"/>
       <c r="C71" s="80"/>
-      <c r="D71" s="199"/>
-      <c r="E71" s="199"/>
-      <c r="F71" s="199"/>
-      <c r="G71" s="199"/>
-      <c r="H71" s="199"/>
-      <c r="I71" s="210"/>
+      <c r="D71" s="175"/>
+      <c r="E71" s="175"/>
+      <c r="F71" s="175"/>
+      <c r="G71" s="175"/>
+      <c r="H71" s="175"/>
+      <c r="I71" s="215"/>
       <c r="J71" s="55" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="93" customHeight="1">
-      <c r="A72" s="246"/>
-      <c r="B72" s="246"/>
+      <c r="A72" s="196"/>
+      <c r="B72" s="196"/>
       <c r="C72" s="80" t="s">
         <v>127</v>
       </c>
-      <c r="D72" s="199"/>
-      <c r="E72" s="199"/>
-      <c r="F72" s="199"/>
-      <c r="G72" s="199"/>
-      <c r="H72" s="199"/>
-      <c r="I72" s="210"/>
+      <c r="D72" s="175"/>
+      <c r="E72" s="175"/>
+      <c r="F72" s="175"/>
+      <c r="G72" s="175"/>
+      <c r="H72" s="175"/>
+      <c r="I72" s="215"/>
       <c r="J72" s="47" t="s">
         <v>289</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="56.25" customHeight="1">
-      <c r="A73" s="246"/>
-      <c r="B73" s="246"/>
+      <c r="A73" s="196"/>
+      <c r="B73" s="196"/>
       <c r="C73" s="80"/>
-      <c r="D73" s="199"/>
-      <c r="E73" s="199"/>
-      <c r="F73" s="199"/>
-      <c r="G73" s="199"/>
-      <c r="H73" s="199"/>
-      <c r="I73" s="210"/>
+      <c r="D73" s="175"/>
+      <c r="E73" s="175"/>
+      <c r="F73" s="175"/>
+      <c r="G73" s="175"/>
+      <c r="H73" s="175"/>
+      <c r="I73" s="215"/>
       <c r="J73" s="55" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="74" spans="1:10" ht="86.25" customHeight="1">
-      <c r="A74" s="246"/>
-      <c r="B74" s="246"/>
+      <c r="A74" s="196"/>
+      <c r="B74" s="196"/>
       <c r="C74" s="80" t="s">
         <v>126</v>
       </c>
-      <c r="D74" s="199"/>
-      <c r="E74" s="199"/>
-      <c r="F74" s="199"/>
-      <c r="G74" s="199"/>
-      <c r="H74" s="199"/>
-      <c r="I74" s="210"/>
+      <c r="D74" s="175"/>
+      <c r="E74" s="175"/>
+      <c r="F74" s="175"/>
+      <c r="G74" s="175"/>
+      <c r="H74" s="175"/>
+      <c r="I74" s="215"/>
       <c r="J74" s="53" t="s">
         <v>291</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="72">
-      <c r="A75" s="246" t="s">
+      <c r="A75" s="196" t="s">
         <v>35</v>
       </c>
-      <c r="B75" s="246"/>
+      <c r="B75" s="196"/>
       <c r="C75" s="74"/>
       <c r="D75" s="116" t="s">
         <v>250</v>
@@ -13262,10 +13262,10 @@
       </c>
     </row>
     <row r="76" spans="1:10" ht="72" customHeight="1">
-      <c r="A76" s="246" t="s">
+      <c r="A76" s="196" t="s">
         <v>46</v>
       </c>
-      <c r="B76" s="246"/>
+      <c r="B76" s="196"/>
       <c r="C76" s="74" t="s">
         <v>47</v>
       </c>
@@ -13311,35 +13311,35 @@
       <c r="C79" s="1"/>
     </row>
     <row r="80" spans="1:10" ht="39.75" hidden="1" customHeight="1">
-      <c r="A80" s="238" t="s">
+      <c r="A80" s="205" t="s">
         <v>22</v>
       </c>
-      <c r="B80" s="238"/>
-      <c r="C80" s="238" t="s">
+      <c r="B80" s="205"/>
+      <c r="C80" s="205" t="s">
         <v>6</v>
       </c>
-      <c r="D80" s="249" t="s">
+      <c r="D80" s="224" t="s">
         <v>7</v>
       </c>
-      <c r="E80" s="249"/>
-      <c r="F80" s="249" t="s">
+      <c r="E80" s="224"/>
+      <c r="F80" s="224" t="s">
         <v>8</v>
       </c>
-      <c r="G80" s="249"/>
-      <c r="H80" s="250" t="s">
+      <c r="G80" s="224"/>
+      <c r="H80" s="216" t="s">
         <v>9</v>
       </c>
-      <c r="I80" s="238" t="s">
+      <c r="I80" s="205" t="s">
         <v>2</v>
       </c>
-      <c r="J80" s="248" t="s">
+      <c r="J80" s="203" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="81" spans="1:10" ht="39.75" hidden="1" customHeight="1">
-      <c r="A81" s="238"/>
-      <c r="B81" s="238"/>
-      <c r="C81" s="238"/>
+      <c r="A81" s="205"/>
+      <c r="B81" s="205"/>
+      <c r="C81" s="205"/>
       <c r="D81" s="6" t="s">
         <v>3</v>
       </c>
@@ -13352,18 +13352,18 @@
       <c r="G81" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H81" s="250"/>
-      <c r="I81" s="238"/>
-      <c r="J81" s="248"/>
+      <c r="H81" s="216"/>
+      <c r="I81" s="205"/>
+      <c r="J81" s="203"/>
     </row>
     <row r="82" spans="1:10" ht="91.5" hidden="1" customHeight="1">
-      <c r="A82" s="236" t="s">
+      <c r="A82" s="217" t="s">
         <v>59</v>
       </c>
       <c r="B82" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="C82" s="179" t="s">
+      <c r="C82" s="220" t="s">
         <v>99</v>
       </c>
       <c r="D82" s="19" t="s">
@@ -13381,7 +13381,7 @@
       <c r="H82" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="I82" s="181" t="s">
+      <c r="I82" s="222" t="s">
         <v>100</v>
       </c>
       <c r="J82" s="118" t="s">
@@ -13389,11 +13389,11 @@
       </c>
     </row>
     <row r="83" spans="1:10" ht="124.5" hidden="1" customHeight="1">
-      <c r="A83" s="239"/>
+      <c r="A83" s="218"/>
       <c r="B83" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="C83" s="180"/>
+      <c r="C83" s="221"/>
       <c r="D83" s="23" t="s">
         <v>5</v>
       </c>
@@ -13409,13 +13409,13 @@
       <c r="H83" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I83" s="182"/>
+      <c r="I83" s="223"/>
       <c r="J83" s="119" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="84" spans="1:10" ht="91.5" hidden="1" customHeight="1">
-      <c r="A84" s="237"/>
+      <c r="A84" s="219"/>
       <c r="B84" s="28" t="s">
         <v>114</v>
       </c>
@@ -13445,10 +13445,10 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="246.75" hidden="1" customHeight="1">
-      <c r="A85" s="244" t="s">
+      <c r="A85" s="225" t="s">
         <v>50</v>
       </c>
-      <c r="B85" s="244"/>
+      <c r="B85" s="225"/>
       <c r="C85" s="25"/>
       <c r="D85" s="24"/>
       <c r="E85" s="24"/>
@@ -13707,24 +13707,68 @@
     <filterColumn colId="0" showButton="0"/>
   </autoFilter>
   <mergeCells count="96">
-    <mergeCell ref="E34:E36"/>
-    <mergeCell ref="A32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="E20:E21"/>
-    <mergeCell ref="F20:F21"/>
-    <mergeCell ref="D20:D21"/>
-    <mergeCell ref="A11:B14"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="A31:B31"/>
-    <mergeCell ref="G11:G14"/>
-    <mergeCell ref="H11:H14"/>
-    <mergeCell ref="F11:F14"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="E11:E14"/>
-    <mergeCell ref="A15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="J15:J16"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="G22:G23"/>
+    <mergeCell ref="H22:H23"/>
+    <mergeCell ref="I22:I23"/>
+    <mergeCell ref="A22:B23"/>
+    <mergeCell ref="C22:C23"/>
+    <mergeCell ref="D22:D23"/>
+    <mergeCell ref="E22:E23"/>
+    <mergeCell ref="F22:F23"/>
+    <mergeCell ref="G20:G21"/>
+    <mergeCell ref="H20:H21"/>
+    <mergeCell ref="A20:B21"/>
+    <mergeCell ref="C20:C21"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A85:B85"/>
+    <mergeCell ref="I40:I41"/>
+    <mergeCell ref="D40:D41"/>
+    <mergeCell ref="E40:E41"/>
+    <mergeCell ref="A40:B41"/>
+    <mergeCell ref="C40:C41"/>
+    <mergeCell ref="F40:F41"/>
+    <mergeCell ref="G40:G41"/>
+    <mergeCell ref="H40:H41"/>
+    <mergeCell ref="I80:I81"/>
+    <mergeCell ref="H66:H74"/>
+    <mergeCell ref="I66:I74"/>
+    <mergeCell ref="D66:D74"/>
+    <mergeCell ref="E66:E74"/>
+    <mergeCell ref="F66:F74"/>
+    <mergeCell ref="G66:G74"/>
+    <mergeCell ref="J80:J81"/>
+    <mergeCell ref="A82:A84"/>
+    <mergeCell ref="C82:C83"/>
+    <mergeCell ref="I82:I83"/>
+    <mergeCell ref="A80:B81"/>
+    <mergeCell ref="C80:C81"/>
+    <mergeCell ref="D80:E80"/>
+    <mergeCell ref="F80:G80"/>
+    <mergeCell ref="H80:H81"/>
+    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A66:B74"/>
+    <mergeCell ref="C66:C69"/>
+    <mergeCell ref="I42:I65"/>
+    <mergeCell ref="A46:A65"/>
+    <mergeCell ref="I34:I36"/>
+    <mergeCell ref="H34:H36"/>
+    <mergeCell ref="G42:G45"/>
+    <mergeCell ref="G34:G36"/>
+    <mergeCell ref="A42:A45"/>
+    <mergeCell ref="I37:I39"/>
+    <mergeCell ref="D42:D45"/>
+    <mergeCell ref="E42:E45"/>
+    <mergeCell ref="F42:F45"/>
+    <mergeCell ref="H42:H45"/>
+    <mergeCell ref="A34:A39"/>
+    <mergeCell ref="B34:B36"/>
+    <mergeCell ref="B37:B39"/>
+    <mergeCell ref="C34:C36"/>
+    <mergeCell ref="F34:F36"/>
+    <mergeCell ref="D34:D36"/>
     <mergeCell ref="I32:I33"/>
     <mergeCell ref="A1:J2"/>
     <mergeCell ref="H8:H9"/>
@@ -13741,68 +13785,24 @@
     <mergeCell ref="A10:B10"/>
     <mergeCell ref="A24:B26"/>
     <mergeCell ref="C24:C25"/>
-    <mergeCell ref="I34:I36"/>
-    <mergeCell ref="H34:H36"/>
-    <mergeCell ref="G42:G45"/>
-    <mergeCell ref="G34:G36"/>
-    <mergeCell ref="A42:A45"/>
-    <mergeCell ref="I37:I39"/>
-    <mergeCell ref="D42:D45"/>
-    <mergeCell ref="E42:E45"/>
-    <mergeCell ref="F42:F45"/>
-    <mergeCell ref="H42:H45"/>
-    <mergeCell ref="A34:A39"/>
-    <mergeCell ref="B34:B36"/>
-    <mergeCell ref="B37:B39"/>
-    <mergeCell ref="C34:C36"/>
-    <mergeCell ref="F34:F36"/>
-    <mergeCell ref="D34:D36"/>
-    <mergeCell ref="A75:B75"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A66:B74"/>
-    <mergeCell ref="C66:C69"/>
-    <mergeCell ref="I42:I65"/>
-    <mergeCell ref="A46:A65"/>
-    <mergeCell ref="J80:J81"/>
-    <mergeCell ref="A82:A84"/>
-    <mergeCell ref="C82:C83"/>
-    <mergeCell ref="I82:I83"/>
-    <mergeCell ref="A80:B81"/>
-    <mergeCell ref="C80:C81"/>
-    <mergeCell ref="D80:E80"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="H80:H81"/>
-    <mergeCell ref="A85:B85"/>
-    <mergeCell ref="I40:I41"/>
-    <mergeCell ref="D40:D41"/>
-    <mergeCell ref="E40:E41"/>
-    <mergeCell ref="A40:B41"/>
-    <mergeCell ref="C40:C41"/>
-    <mergeCell ref="F40:F41"/>
-    <mergeCell ref="G40:G41"/>
-    <mergeCell ref="H40:H41"/>
-    <mergeCell ref="I80:I81"/>
-    <mergeCell ref="H66:H74"/>
-    <mergeCell ref="I66:I74"/>
-    <mergeCell ref="D66:D74"/>
-    <mergeCell ref="E66:E74"/>
-    <mergeCell ref="F66:F74"/>
-    <mergeCell ref="G66:G74"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="G22:G23"/>
-    <mergeCell ref="H22:H23"/>
-    <mergeCell ref="I22:I23"/>
-    <mergeCell ref="A22:B23"/>
-    <mergeCell ref="C22:C23"/>
-    <mergeCell ref="D22:D23"/>
-    <mergeCell ref="E22:E23"/>
-    <mergeCell ref="F22:F23"/>
-    <mergeCell ref="G20:G21"/>
-    <mergeCell ref="H20:H21"/>
-    <mergeCell ref="A20:B21"/>
-    <mergeCell ref="C20:C21"/>
-    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A11:B14"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="A31:B31"/>
+    <mergeCell ref="G11:G14"/>
+    <mergeCell ref="H11:H14"/>
+    <mergeCell ref="F11:F14"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="E11:E14"/>
+    <mergeCell ref="A15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B19"/>
+    <mergeCell ref="E34:E36"/>
+    <mergeCell ref="A32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="E20:E21"/>
+    <mergeCell ref="F20:F21"/>
+    <mergeCell ref="D20:D21"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
@@ -13838,28 +13838,28 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
-      <c r="A1" s="255"/>
-      <c r="B1" s="255"/>
-      <c r="C1" s="255"/>
-      <c r="D1" s="255"/>
-      <c r="E1" s="255"/>
-      <c r="F1" s="255"/>
-      <c r="G1" s="255"/>
-      <c r="H1" s="255"/>
-      <c r="I1" s="255"/>
-      <c r="J1" s="255"/>
+      <c r="A1" s="234"/>
+      <c r="B1" s="234"/>
+      <c r="C1" s="234"/>
+      <c r="D1" s="234"/>
+      <c r="E1" s="234"/>
+      <c r="F1" s="234"/>
+      <c r="G1" s="234"/>
+      <c r="H1" s="234"/>
+      <c r="I1" s="234"/>
+      <c r="J1" s="234"/>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="255"/>
-      <c r="B2" s="255"/>
-      <c r="C2" s="255"/>
-      <c r="D2" s="255"/>
-      <c r="E2" s="255"/>
-      <c r="F2" s="255"/>
-      <c r="G2" s="255"/>
-      <c r="H2" s="255"/>
-      <c r="I2" s="255"/>
-      <c r="J2" s="255"/>
+      <c r="A2" s="234"/>
+      <c r="B2" s="234"/>
+      <c r="C2" s="234"/>
+      <c r="D2" s="234"/>
+      <c r="E2" s="234"/>
+      <c r="F2" s="234"/>
+      <c r="G2" s="234"/>
+      <c r="H2" s="234"/>
+      <c r="I2" s="234"/>
+      <c r="J2" s="234"/>
     </row>
     <row r="3" spans="1:10" ht="17">
       <c r="A3" s="32" t="s">
@@ -13927,35 +13927,35 @@
       </c>
     </row>
     <row r="8" spans="1:10" ht="25.5" customHeight="1">
-      <c r="A8" s="248" t="s">
+      <c r="A8" s="203" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="248"/>
-      <c r="C8" s="248" t="s">
+      <c r="B8" s="203"/>
+      <c r="C8" s="203" t="s">
         <v>6</v>
       </c>
-      <c r="D8" s="248" t="s">
+      <c r="D8" s="203" t="s">
         <v>7</v>
       </c>
-      <c r="E8" s="248"/>
-      <c r="F8" s="248" t="s">
+      <c r="E8" s="203"/>
+      <c r="F8" s="203" t="s">
         <v>8</v>
       </c>
-      <c r="G8" s="248"/>
-      <c r="H8" s="183" t="s">
+      <c r="G8" s="203"/>
+      <c r="H8" s="204" t="s">
         <v>9</v>
       </c>
-      <c r="I8" s="248" t="s">
+      <c r="I8" s="203" t="s">
         <v>2</v>
       </c>
-      <c r="J8" s="238" t="s">
+      <c r="J8" s="205" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="9" spans="1:10" ht="25.5" customHeight="1">
-      <c r="A9" s="248"/>
-      <c r="B9" s="248"/>
-      <c r="C9" s="248"/>
+      <c r="A9" s="203"/>
+      <c r="B9" s="203"/>
+      <c r="C9" s="203"/>
       <c r="D9" s="63" t="s">
         <v>3</v>
       </c>
@@ -13968,15 +13968,15 @@
       <c r="G9" s="63" t="s">
         <v>4</v>
       </c>
-      <c r="H9" s="183"/>
-      <c r="I9" s="248"/>
-      <c r="J9" s="238"/>
+      <c r="H9" s="204"/>
+      <c r="I9" s="203"/>
+      <c r="J9" s="205"/>
     </row>
     <row r="10" spans="1:10" ht="244.5" customHeight="1">
-      <c r="A10" s="229" t="s">
+      <c r="A10" s="226" t="s">
         <v>293</v>
       </c>
-      <c r="B10" s="229"/>
+      <c r="B10" s="226"/>
       <c r="C10" s="74" t="s">
         <v>294</v>
       </c>
@@ -14003,29 +14003,29 @@
       </c>
     </row>
     <row r="11" spans="1:10" ht="90" customHeight="1">
-      <c r="A11" s="243" t="s">
+      <c r="A11" s="195" t="s">
         <v>33</v>
       </c>
-      <c r="B11" s="243"/>
-      <c r="C11" s="202" t="s">
+      <c r="B11" s="195"/>
+      <c r="C11" s="197" t="s">
         <v>296</v>
       </c>
-      <c r="D11" s="279" t="s">
+      <c r="D11" s="206" t="s">
         <v>5</v>
       </c>
-      <c r="E11" s="279" t="s">
+      <c r="E11" s="206" t="s">
         <v>5</v>
       </c>
-      <c r="F11" s="279" t="s">
+      <c r="F11" s="206" t="s">
         <v>5</v>
       </c>
-      <c r="G11" s="279" t="s">
+      <c r="G11" s="206" t="s">
         <v>5</v>
       </c>
-      <c r="H11" s="279" t="s">
+      <c r="H11" s="206" t="s">
         <v>5</v>
       </c>
-      <c r="I11" s="256" t="s">
+      <c r="I11" s="207" t="s">
         <v>39</v>
       </c>
       <c r="J11" s="130" t="s">
@@ -14033,94 +14033,94 @@
       </c>
     </row>
     <row r="12" spans="1:10" ht="48">
-      <c r="A12" s="243"/>
-      <c r="B12" s="243"/>
-      <c r="C12" s="202"/>
-      <c r="D12" s="279"/>
-      <c r="E12" s="279"/>
-      <c r="F12" s="279"/>
-      <c r="G12" s="279"/>
-      <c r="H12" s="279"/>
-      <c r="I12" s="257"/>
+      <c r="A12" s="195"/>
+      <c r="B12" s="195"/>
+      <c r="C12" s="197"/>
+      <c r="D12" s="206"/>
+      <c r="E12" s="206"/>
+      <c r="F12" s="206"/>
+      <c r="G12" s="206"/>
+      <c r="H12" s="206"/>
+      <c r="I12" s="208"/>
       <c r="J12" s="125" t="s">
         <v>278</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="128">
-      <c r="A13" s="243"/>
-      <c r="B13" s="243"/>
-      <c r="C13" s="202"/>
-      <c r="D13" s="279"/>
-      <c r="E13" s="279"/>
-      <c r="F13" s="279"/>
-      <c r="G13" s="279"/>
-      <c r="H13" s="279"/>
-      <c r="I13" s="257"/>
+      <c r="A13" s="195"/>
+      <c r="B13" s="195"/>
+      <c r="C13" s="197"/>
+      <c r="D13" s="206"/>
+      <c r="E13" s="206"/>
+      <c r="F13" s="206"/>
+      <c r="G13" s="206"/>
+      <c r="H13" s="206"/>
+      <c r="I13" s="208"/>
       <c r="J13" s="125" t="s">
         <v>298</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="51.75" customHeight="1">
-      <c r="A14" s="243"/>
-      <c r="B14" s="243"/>
-      <c r="C14" s="202"/>
-      <c r="D14" s="279"/>
-      <c r="E14" s="279"/>
-      <c r="F14" s="279"/>
-      <c r="G14" s="279"/>
-      <c r="H14" s="279"/>
-      <c r="I14" s="257"/>
+      <c r="A14" s="195"/>
+      <c r="B14" s="195"/>
+      <c r="C14" s="197"/>
+      <c r="D14" s="206"/>
+      <c r="E14" s="206"/>
+      <c r="F14" s="206"/>
+      <c r="G14" s="206"/>
+      <c r="H14" s="206"/>
+      <c r="I14" s="208"/>
       <c r="J14" s="126" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:10" ht="61.5" customHeight="1">
-      <c r="A15" s="248" t="s">
+      <c r="A15" s="203" t="s">
         <v>48</v>
       </c>
-      <c r="B15" s="248"/>
-      <c r="C15" s="202" t="s">
+      <c r="B15" s="203"/>
+      <c r="C15" s="197" t="s">
         <v>296</v>
       </c>
-      <c r="D15" s="274" t="s">
+      <c r="D15" s="209" t="s">
         <v>0</v>
       </c>
-      <c r="E15" s="274" t="s">
+      <c r="E15" s="209" t="s">
         <v>0</v>
       </c>
-      <c r="F15" s="274" t="s">
+      <c r="F15" s="209" t="s">
         <v>0</v>
       </c>
-      <c r="G15" s="274" t="s">
+      <c r="G15" s="209" t="s">
         <v>0</v>
       </c>
-      <c r="H15" s="275" t="s">
+      <c r="H15" s="233" t="s">
         <v>0</v>
       </c>
-      <c r="I15" s="242" t="s">
+      <c r="I15" s="214" t="s">
         <v>281</v>
       </c>
-      <c r="J15" s="242" t="s">
+      <c r="J15" s="214" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="16" spans="1:10" ht="60.75" customHeight="1">
-      <c r="A16" s="248"/>
-      <c r="B16" s="248"/>
-      <c r="C16" s="202"/>
-      <c r="D16" s="274"/>
-      <c r="E16" s="274"/>
-      <c r="F16" s="274"/>
-      <c r="G16" s="274"/>
-      <c r="H16" s="275"/>
-      <c r="I16" s="242"/>
-      <c r="J16" s="242"/>
+      <c r="A16" s="203"/>
+      <c r="B16" s="203"/>
+      <c r="C16" s="197"/>
+      <c r="D16" s="209"/>
+      <c r="E16" s="209"/>
+      <c r="F16" s="209"/>
+      <c r="G16" s="209"/>
+      <c r="H16" s="233"/>
+      <c r="I16" s="214"/>
+      <c r="J16" s="214"/>
     </row>
     <row r="17" spans="1:10" ht="153.75" customHeight="1">
-      <c r="A17" s="248" t="s">
+      <c r="A17" s="203" t="s">
         <v>34</v>
       </c>
-      <c r="B17" s="248"/>
+      <c r="B17" s="203"/>
       <c r="C17" s="74" t="s">
         <v>36</v>
       </c>
@@ -14137,10 +14137,10 @@
       </c>
     </row>
     <row r="18" spans="1:10" ht="245.25" customHeight="1">
-      <c r="A18" s="243" t="s">
+      <c r="A18" s="195" t="s">
         <v>40</v>
       </c>
-      <c r="B18" s="243"/>
+      <c r="B18" s="195"/>
       <c r="C18" s="74" t="s">
         <v>41</v>
       </c>
@@ -14157,50 +14157,50 @@
       </c>
     </row>
     <row r="19" spans="1:10" ht="188.25" customHeight="1">
-      <c r="A19" s="276" t="s">
+      <c r="A19" s="236" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="276"/>
-      <c r="C19" s="202" t="s">
+      <c r="B19" s="236"/>
+      <c r="C19" s="197" t="s">
         <v>303</v>
       </c>
-      <c r="D19" s="277"/>
-      <c r="E19" s="277"/>
-      <c r="F19" s="277"/>
-      <c r="G19" s="277"/>
-      <c r="H19" s="277"/>
-      <c r="I19" s="280" t="s">
+      <c r="D19" s="213"/>
+      <c r="E19" s="213"/>
+      <c r="F19" s="213"/>
+      <c r="G19" s="213"/>
+      <c r="H19" s="213"/>
+      <c r="I19" s="210" t="s">
         <v>304</v>
       </c>
-      <c r="J19" s="282" t="s">
+      <c r="J19" s="212" t="s">
         <v>319</v>
       </c>
     </row>
     <row r="20" spans="1:10" ht="164.25" customHeight="1">
-      <c r="A20" s="276"/>
-      <c r="B20" s="276"/>
-      <c r="C20" s="202"/>
-      <c r="D20" s="277"/>
-      <c r="E20" s="277"/>
-      <c r="F20" s="277"/>
-      <c r="G20" s="277"/>
-      <c r="H20" s="277"/>
-      <c r="I20" s="281"/>
-      <c r="J20" s="282"/>
+      <c r="A20" s="236"/>
+      <c r="B20" s="236"/>
+      <c r="C20" s="197"/>
+      <c r="D20" s="213"/>
+      <c r="E20" s="213"/>
+      <c r="F20" s="213"/>
+      <c r="G20" s="213"/>
+      <c r="H20" s="213"/>
+      <c r="I20" s="211"/>
+      <c r="J20" s="212"/>
     </row>
     <row r="21" spans="1:10" ht="64.5" customHeight="1">
-      <c r="A21" s="248" t="s">
+      <c r="A21" s="203" t="s">
         <v>42</v>
       </c>
-      <c r="B21" s="248"/>
-      <c r="C21" s="202" t="s">
+      <c r="B21" s="203"/>
+      <c r="C21" s="197" t="s">
         <v>36</v>
       </c>
-      <c r="D21" s="274"/>
-      <c r="E21" s="274"/>
-      <c r="F21" s="274"/>
-      <c r="G21" s="274"/>
-      <c r="H21" s="274"/>
+      <c r="D21" s="209"/>
+      <c r="E21" s="209"/>
+      <c r="F21" s="209"/>
+      <c r="G21" s="209"/>
+      <c r="H21" s="209"/>
       <c r="I21" s="122" t="s">
         <v>43</v>
       </c>
@@ -14209,14 +14209,14 @@
       </c>
     </row>
     <row r="22" spans="1:10" ht="41.25" customHeight="1">
-      <c r="A22" s="248"/>
-      <c r="B22" s="248"/>
-      <c r="C22" s="202"/>
-      <c r="D22" s="274"/>
-      <c r="E22" s="274"/>
-      <c r="F22" s="274"/>
-      <c r="G22" s="274"/>
-      <c r="H22" s="274"/>
+      <c r="A22" s="203"/>
+      <c r="B22" s="203"/>
+      <c r="C22" s="197"/>
+      <c r="D22" s="209"/>
+      <c r="E22" s="209"/>
+      <c r="F22" s="209"/>
+      <c r="G22" s="209"/>
+      <c r="H22" s="209"/>
       <c r="I22" s="122" t="s">
         <v>44</v>
       </c>
@@ -14225,27 +14225,27 @@
       </c>
     </row>
     <row r="23" spans="1:10" ht="39" customHeight="1">
-      <c r="A23" s="246" t="s">
+      <c r="A23" s="196" t="s">
         <v>21</v>
       </c>
-      <c r="B23" s="246"/>
-      <c r="C23" s="202" t="s">
+      <c r="B23" s="196"/>
+      <c r="C23" s="197" t="s">
         <v>23</v>
       </c>
-      <c r="D23" s="271" t="s">
+      <c r="D23" s="237" t="s">
         <v>5</v>
       </c>
-      <c r="E23" s="271" t="s">
+      <c r="E23" s="237" t="s">
         <v>5</v>
       </c>
-      <c r="F23" s="271" t="s">
+      <c r="F23" s="237" t="s">
         <v>5</v>
       </c>
-      <c r="G23" s="271" t="s">
+      <c r="G23" s="237" t="s">
         <v>5</v>
       </c>
-      <c r="H23" s="278"/>
-      <c r="I23" s="266" t="s">
+      <c r="H23" s="238"/>
+      <c r="I23" s="239" t="s">
         <v>305</v>
       </c>
       <c r="J23" s="130" t="s">
@@ -14253,24 +14253,24 @@
       </c>
     </row>
     <row r="24" spans="1:10" ht="28.5" customHeight="1">
-      <c r="A24" s="246"/>
-      <c r="B24" s="246"/>
-      <c r="C24" s="202"/>
-      <c r="D24" s="271"/>
-      <c r="E24" s="271"/>
-      <c r="F24" s="271"/>
-      <c r="G24" s="271"/>
-      <c r="H24" s="278"/>
-      <c r="I24" s="266"/>
+      <c r="A24" s="196"/>
+      <c r="B24" s="196"/>
+      <c r="C24" s="197"/>
+      <c r="D24" s="237"/>
+      <c r="E24" s="237"/>
+      <c r="F24" s="237"/>
+      <c r="G24" s="237"/>
+      <c r="H24" s="238"/>
+      <c r="I24" s="239"/>
       <c r="J24" s="138" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:10" s="62" customFormat="1" ht="219.75" customHeight="1">
-      <c r="A25" s="211" t="s">
+      <c r="A25" s="227" t="s">
         <v>199</v>
       </c>
-      <c r="B25" s="212"/>
+      <c r="B25" s="190"/>
       <c r="C25" s="170" t="s">
         <v>207</v>
       </c>
@@ -14295,25 +14295,25 @@
       </c>
     </row>
     <row r="26" spans="1:10" s="62" customFormat="1" ht="133.5" customHeight="1">
-      <c r="A26" s="211"/>
-      <c r="B26" s="212"/>
-      <c r="C26" s="269" t="s">
+      <c r="A26" s="227"/>
+      <c r="B26" s="190"/>
+      <c r="C26" s="230" t="s">
         <v>202</v>
       </c>
-      <c r="D26" s="217" t="s">
+      <c r="D26" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="E26" s="217" t="s">
+      <c r="E26" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="F26" s="217" t="s">
+      <c r="F26" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="G26" s="217" t="s">
+      <c r="G26" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="H26" s="272"/>
-      <c r="I26" s="184" t="s">
+      <c r="H26" s="184"/>
+      <c r="I26" s="201" t="s">
         <v>307</v>
       </c>
       <c r="J26" s="136" t="s">
@@ -14321,29 +14321,29 @@
       </c>
     </row>
     <row r="27" spans="1:10" s="62" customFormat="1" ht="35.25" customHeight="1">
-      <c r="A27" s="211"/>
-      <c r="B27" s="212"/>
-      <c r="C27" s="270"/>
-      <c r="D27" s="218"/>
-      <c r="E27" s="218"/>
-      <c r="F27" s="218"/>
-      <c r="G27" s="218"/>
-      <c r="H27" s="273"/>
-      <c r="I27" s="185"/>
+      <c r="A27" s="227"/>
+      <c r="B27" s="190"/>
+      <c r="C27" s="231"/>
+      <c r="D27" s="183"/>
+      <c r="E27" s="183"/>
+      <c r="F27" s="183"/>
+      <c r="G27" s="183"/>
+      <c r="H27" s="185"/>
+      <c r="I27" s="202"/>
       <c r="J27" s="72" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="28" spans="1:10" s="62" customFormat="1" ht="154.5" customHeight="1">
-      <c r="A28" s="211"/>
-      <c r="B28" s="212"/>
-      <c r="C28" s="267" t="s">
+      <c r="A28" s="227"/>
+      <c r="B28" s="190"/>
+      <c r="C28" s="240" t="s">
         <v>306</v>
       </c>
-      <c r="D28" s="236" t="s">
+      <c r="D28" s="217" t="s">
         <v>5</v>
       </c>
-      <c r="E28" s="236" t="s">
+      <c r="E28" s="217" t="s">
         <v>5</v>
       </c>
       <c r="F28" s="68" t="s">
@@ -14353,7 +14353,7 @@
         <v>5</v>
       </c>
       <c r="H28" s="69"/>
-      <c r="I28" s="240" t="s">
+      <c r="I28" s="242" t="s">
         <v>210</v>
       </c>
       <c r="J28" s="15" t="s">
@@ -14361,11 +14361,11 @@
       </c>
     </row>
     <row r="29" spans="1:10" s="62" customFormat="1" ht="33" customHeight="1">
-      <c r="A29" s="213"/>
-      <c r="B29" s="214"/>
-      <c r="C29" s="268"/>
-      <c r="D29" s="237"/>
-      <c r="E29" s="237"/>
+      <c r="A29" s="228"/>
+      <c r="B29" s="229"/>
+      <c r="C29" s="241"/>
+      <c r="D29" s="219"/>
+      <c r="E29" s="219"/>
       <c r="F29" s="24" t="s">
         <v>5</v>
       </c>
@@ -14373,33 +14373,33 @@
         <v>5</v>
       </c>
       <c r="H29" s="21"/>
-      <c r="I29" s="241"/>
+      <c r="I29" s="243"/>
       <c r="J29" s="70" t="s">
         <v>200</v>
       </c>
     </row>
     <row r="30" spans="1:10" s="62" customFormat="1" ht="133.5" customHeight="1">
-      <c r="A30" s="211" t="s">
+      <c r="A30" s="227" t="s">
         <v>201</v>
       </c>
-      <c r="B30" s="212"/>
-      <c r="C30" s="269" t="s">
+      <c r="B30" s="190"/>
+      <c r="C30" s="230" t="s">
         <v>202</v>
       </c>
-      <c r="D30" s="217" t="s">
+      <c r="D30" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="E30" s="217" t="s">
+      <c r="E30" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="F30" s="217" t="s">
+      <c r="F30" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="G30" s="217" t="s">
+      <c r="G30" s="182" t="s">
         <v>5</v>
       </c>
-      <c r="H30" s="272"/>
-      <c r="I30" s="184" t="s">
+      <c r="H30" s="184"/>
+      <c r="I30" s="201" t="s">
         <v>307</v>
       </c>
       <c r="J30" s="136" t="s">
@@ -14407,25 +14407,25 @@
       </c>
     </row>
     <row r="31" spans="1:10" s="62" customFormat="1" ht="35.25" customHeight="1">
-      <c r="A31" s="213"/>
-      <c r="B31" s="214"/>
-      <c r="C31" s="270"/>
-      <c r="D31" s="218"/>
-      <c r="E31" s="218"/>
-      <c r="F31" s="218"/>
-      <c r="G31" s="218"/>
-      <c r="H31" s="273"/>
-      <c r="I31" s="185"/>
+      <c r="A31" s="228"/>
+      <c r="B31" s="229"/>
+      <c r="C31" s="231"/>
+      <c r="D31" s="183"/>
+      <c r="E31" s="183"/>
+      <c r="F31" s="183"/>
+      <c r="G31" s="183"/>
+      <c r="H31" s="185"/>
+      <c r="I31" s="202"/>
       <c r="J31" s="72" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="32" spans="1:10" ht="108.75" customHeight="1">
-      <c r="A32" s="246" t="s">
+      <c r="A32" s="196" t="s">
         <v>16</v>
       </c>
-      <c r="B32" s="246"/>
-      <c r="C32" s="202"/>
+      <c r="B32" s="196"/>
+      <c r="C32" s="197"/>
       <c r="D32" s="113"/>
       <c r="E32" s="91" t="s">
         <v>5</v>
@@ -14433,7 +14433,7 @@
       <c r="F32" s="113"/>
       <c r="G32" s="113"/>
       <c r="H32" s="113"/>
-      <c r="I32" s="193" t="s">
+      <c r="I32" s="181" t="s">
         <v>252</v>
       </c>
       <c r="J32" s="139" t="s">
@@ -14441,24 +14441,24 @@
       </c>
     </row>
     <row r="33" spans="1:10" ht="84" customHeight="1">
-      <c r="A33" s="246"/>
-      <c r="B33" s="246"/>
-      <c r="C33" s="202"/>
+      <c r="A33" s="196"/>
+      <c r="B33" s="196"/>
+      <c r="C33" s="197"/>
       <c r="D33" s="113"/>
       <c r="E33" s="91"/>
       <c r="F33" s="113"/>
       <c r="G33" s="113"/>
       <c r="H33" s="113"/>
-      <c r="I33" s="193"/>
+      <c r="I33" s="181"/>
       <c r="J33" s="140" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="34" spans="1:10" ht="57.75" customHeight="1">
-      <c r="A34" s="258" t="s">
+      <c r="A34" s="187" t="s">
         <v>285</v>
       </c>
-      <c r="B34" s="259"/>
+      <c r="B34" s="188"/>
       <c r="C34" s="160" t="s">
         <v>203</v>
       </c>
@@ -14473,10 +14473,10 @@
       </c>
     </row>
     <row r="35" spans="1:10" ht="87" customHeight="1">
-      <c r="A35" s="260" t="s">
+      <c r="A35" s="189" t="s">
         <v>233</v>
       </c>
-      <c r="B35" s="212"/>
+      <c r="B35" s="190"/>
       <c r="C35" s="158" t="s">
         <v>204</v>
       </c>
@@ -14491,8 +14491,8 @@
       </c>
     </row>
     <row r="36" spans="1:10" ht="143.25" customHeight="1">
-      <c r="A36" s="261"/>
-      <c r="B36" s="220"/>
+      <c r="A36" s="191"/>
+      <c r="B36" s="192"/>
       <c r="C36" s="158" t="s">
         <v>205</v>
       </c>
@@ -14509,8 +14509,8 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="15.75" customHeight="1">
-      <c r="A37" s="261"/>
-      <c r="B37" s="220"/>
+      <c r="A37" s="191"/>
+      <c r="B37" s="192"/>
       <c r="C37" s="158"/>
       <c r="D37" s="93"/>
       <c r="E37" s="93"/>
@@ -14523,10 +14523,10 @@
       </c>
     </row>
     <row r="38" spans="1:10" ht="68.25" customHeight="1" thickBot="1">
-      <c r="A38" s="264" t="s">
+      <c r="A38" s="193" t="s">
         <v>237</v>
       </c>
-      <c r="B38" s="265"/>
+      <c r="B38" s="194"/>
       <c r="C38" s="161" t="s">
         <v>206</v>
       </c>
@@ -14541,11 +14541,11 @@
       </c>
     </row>
     <row r="39" spans="1:10" ht="108.75" customHeight="1" thickTop="1">
-      <c r="A39" s="246" t="s">
+      <c r="A39" s="196" t="s">
         <v>16</v>
       </c>
-      <c r="B39" s="246"/>
-      <c r="C39" s="202"/>
+      <c r="B39" s="196"/>
+      <c r="C39" s="197"/>
       <c r="D39" s="113"/>
       <c r="E39" s="91" t="s">
         <v>5</v>
@@ -14553,7 +14553,7 @@
       <c r="F39" s="113"/>
       <c r="G39" s="113"/>
       <c r="H39" s="113"/>
-      <c r="I39" s="193" t="s">
+      <c r="I39" s="181" t="s">
         <v>252</v>
       </c>
       <c r="J39" s="139" t="s">
@@ -14561,37 +14561,37 @@
       </c>
     </row>
     <row r="40" spans="1:10" ht="84" customHeight="1">
-      <c r="A40" s="246"/>
-      <c r="B40" s="246"/>
-      <c r="C40" s="202"/>
+      <c r="A40" s="196"/>
+      <c r="B40" s="196"/>
+      <c r="C40" s="197"/>
       <c r="D40" s="113"/>
       <c r="E40" s="91"/>
       <c r="F40" s="113"/>
       <c r="G40" s="113"/>
       <c r="H40" s="113"/>
-      <c r="I40" s="193"/>
+      <c r="I40" s="181"/>
       <c r="J40" s="140" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="41" spans="1:10" ht="51.75" customHeight="1">
-      <c r="A41" s="243" t="s">
+      <c r="A41" s="195" t="s">
         <v>286</v>
       </c>
-      <c r="B41" s="246" t="s">
+      <c r="B41" s="196" t="s">
         <v>287</v>
       </c>
-      <c r="C41" s="202" t="s">
+      <c r="C41" s="197" t="s">
         <v>26</v>
       </c>
-      <c r="D41" s="199" t="s">
+      <c r="D41" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="E41" s="200"/>
-      <c r="F41" s="200"/>
-      <c r="G41" s="200"/>
-      <c r="H41" s="200"/>
-      <c r="I41" s="208" t="s">
+      <c r="E41" s="186"/>
+      <c r="F41" s="186"/>
+      <c r="G41" s="186"/>
+      <c r="H41" s="186"/>
+      <c r="I41" s="178" t="s">
         <v>253</v>
       </c>
       <c r="J41" s="142" t="s">
@@ -14599,36 +14599,36 @@
       </c>
     </row>
     <row r="42" spans="1:10" ht="16">
-      <c r="A42" s="243"/>
-      <c r="B42" s="246"/>
-      <c r="C42" s="202"/>
-      <c r="D42" s="199"/>
-      <c r="E42" s="200"/>
-      <c r="F42" s="200"/>
-      <c r="G42" s="200"/>
-      <c r="H42" s="200"/>
-      <c r="I42" s="208"/>
+      <c r="A42" s="195"/>
+      <c r="B42" s="196"/>
+      <c r="C42" s="197"/>
+      <c r="D42" s="175"/>
+      <c r="E42" s="186"/>
+      <c r="F42" s="186"/>
+      <c r="G42" s="186"/>
+      <c r="H42" s="186"/>
+      <c r="I42" s="178"/>
       <c r="J42" s="143" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="43" spans="1:10" ht="45.75" customHeight="1">
-      <c r="A43" s="243"/>
-      <c r="B43" s="246"/>
-      <c r="C43" s="202"/>
-      <c r="D43" s="199"/>
-      <c r="E43" s="200"/>
-      <c r="F43" s="200"/>
-      <c r="G43" s="200"/>
-      <c r="H43" s="200"/>
-      <c r="I43" s="208"/>
+      <c r="A43" s="195"/>
+      <c r="B43" s="196"/>
+      <c r="C43" s="197"/>
+      <c r="D43" s="175"/>
+      <c r="E43" s="186"/>
+      <c r="F43" s="186"/>
+      <c r="G43" s="186"/>
+      <c r="H43" s="186"/>
+      <c r="I43" s="178"/>
       <c r="J43" s="142" t="s">
         <v>329</v>
       </c>
     </row>
     <row r="44" spans="1:10" ht="126" customHeight="1">
-      <c r="A44" s="243"/>
-      <c r="B44" s="254" t="s">
+      <c r="A44" s="195"/>
+      <c r="B44" s="198" t="s">
         <v>19</v>
       </c>
       <c r="C44" s="74" t="s">
@@ -14643,7 +14643,7 @@
       </c>
       <c r="G44" s="113"/>
       <c r="H44" s="113"/>
-      <c r="I44" s="208" t="s">
+      <c r="I44" s="178" t="s">
         <v>254</v>
       </c>
       <c r="J44" s="144" t="s">
@@ -14651,8 +14651,8 @@
       </c>
     </row>
     <row r="45" spans="1:10" ht="78.75" customHeight="1">
-      <c r="A45" s="243"/>
-      <c r="B45" s="254"/>
+      <c r="A45" s="195"/>
+      <c r="B45" s="198"/>
       <c r="C45" s="74" t="s">
         <v>156</v>
       </c>
@@ -14661,14 +14661,14 @@
       <c r="F45" s="91"/>
       <c r="G45" s="113"/>
       <c r="H45" s="113"/>
-      <c r="I45" s="208"/>
+      <c r="I45" s="178"/>
       <c r="J45" s="71" t="s">
         <v>331</v>
       </c>
     </row>
     <row r="46" spans="1:10" ht="42.75" customHeight="1">
-      <c r="A46" s="243"/>
-      <c r="B46" s="254"/>
+      <c r="A46" s="195"/>
+      <c r="B46" s="198"/>
       <c r="C46" s="74" t="s">
         <v>26</v>
       </c>
@@ -14681,33 +14681,33 @@
       </c>
       <c r="G46" s="113"/>
       <c r="H46" s="113"/>
-      <c r="I46" s="208"/>
+      <c r="I46" s="178"/>
       <c r="J46" s="151" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="47" spans="1:10" ht="37.5" customHeight="1">
-      <c r="A47" s="246" t="s">
+      <c r="A47" s="196" t="s">
         <v>14</v>
       </c>
-      <c r="B47" s="246"/>
-      <c r="C47" s="202"/>
-      <c r="D47" s="199" t="s">
+      <c r="B47" s="196"/>
+      <c r="C47" s="197"/>
+      <c r="D47" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="E47" s="199" t="s">
+      <c r="E47" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="F47" s="199" t="s">
+      <c r="F47" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="G47" s="199" t="s">
+      <c r="G47" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="H47" s="199" t="s">
+      <c r="H47" s="175" t="s">
         <v>0</v>
       </c>
-      <c r="I47" s="210" t="s">
+      <c r="I47" s="215" t="s">
         <v>140</v>
       </c>
       <c r="J47" s="124" t="s">
@@ -14715,21 +14715,21 @@
       </c>
     </row>
     <row r="48" spans="1:10" ht="27" customHeight="1">
-      <c r="A48" s="246"/>
-      <c r="B48" s="246"/>
-      <c r="C48" s="202"/>
-      <c r="D48" s="199"/>
-      <c r="E48" s="199"/>
-      <c r="F48" s="199"/>
-      <c r="G48" s="199"/>
-      <c r="H48" s="199"/>
-      <c r="I48" s="210"/>
+      <c r="A48" s="196"/>
+      <c r="B48" s="196"/>
+      <c r="C48" s="197"/>
+      <c r="D48" s="175"/>
+      <c r="E48" s="175"/>
+      <c r="F48" s="175"/>
+      <c r="G48" s="175"/>
+      <c r="H48" s="175"/>
+      <c r="I48" s="215"/>
       <c r="J48" s="143" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="49" spans="1:10" ht="94.5" customHeight="1">
-      <c r="A49" s="253" t="s">
+      <c r="A49" s="200" t="s">
         <v>84</v>
       </c>
       <c r="B49" s="79" t="s">
@@ -14738,22 +14738,22 @@
       <c r="C49" s="74" t="s">
         <v>11</v>
       </c>
-      <c r="D49" s="199" t="s">
+      <c r="D49" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="E49" s="199" t="s">
+      <c r="E49" s="175" t="s">
         <v>5</v>
       </c>
-      <c r="F49" s="199" t="s">
+      <c r="F49" s="175" t="s">
         <v>244</v>
       </c>
-      <c r="G49" s="199" t="s">
+      <c r="G49" s="175" t="s">
         <v>244</v>
       </c>
-      <c r="H49" s="199" t="s">
+      <c r="H49" s="175" t="s">
         <v>244</v>
       </c>
-      <c r="I49" s="252" t="s">
+      <c r="I49" s="199" t="s">
         <v>255</v>
       </c>
       <c r="J49" s="135" t="s">
@@ -14761,55 +14761,55 @@
       </c>
     </row>
     <row r="50" spans="1:10" ht="345" customHeight="1">
-      <c r="A50" s="253"/>
+      <c r="A50" s="200"/>
       <c r="B50" s="79" t="s">
         <v>12</v>
       </c>
       <c r="C50" s="74"/>
-      <c r="D50" s="199"/>
-      <c r="E50" s="199"/>
-      <c r="F50" s="199"/>
-      <c r="G50" s="199"/>
-      <c r="H50" s="199"/>
-      <c r="I50" s="252"/>
+      <c r="D50" s="175"/>
+      <c r="E50" s="175"/>
+      <c r="F50" s="175"/>
+      <c r="G50" s="175"/>
+      <c r="H50" s="175"/>
+      <c r="I50" s="199"/>
       <c r="J50" s="45" t="s">
         <v>359</v>
       </c>
     </row>
     <row r="51" spans="1:10" ht="80.25" customHeight="1">
-      <c r="A51" s="253"/>
+      <c r="A51" s="200"/>
       <c r="B51" s="79" t="s">
         <v>132</v>
       </c>
       <c r="C51" s="74"/>
-      <c r="D51" s="199"/>
-      <c r="E51" s="199"/>
-      <c r="F51" s="199"/>
-      <c r="G51" s="199"/>
-      <c r="H51" s="199"/>
-      <c r="I51" s="252"/>
+      <c r="D51" s="175"/>
+      <c r="E51" s="175"/>
+      <c r="F51" s="175"/>
+      <c r="G51" s="175"/>
+      <c r="H51" s="175"/>
+      <c r="I51" s="199"/>
       <c r="J51" s="135" t="s">
         <v>333</v>
       </c>
     </row>
     <row r="52" spans="1:10" ht="52.5" customHeight="1">
-      <c r="A52" s="253"/>
+      <c r="A52" s="200"/>
       <c r="B52" s="79" t="s">
         <v>13</v>
       </c>
       <c r="C52" s="74"/>
-      <c r="D52" s="199"/>
-      <c r="E52" s="199"/>
-      <c r="F52" s="199"/>
-      <c r="G52" s="199"/>
-      <c r="H52" s="199"/>
-      <c r="I52" s="252"/>
+      <c r="D52" s="175"/>
+      <c r="E52" s="175"/>
+      <c r="F52" s="175"/>
+      <c r="G52" s="175"/>
+      <c r="H52" s="175"/>
+      <c r="I52" s="199"/>
       <c r="J52" s="145" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="53" spans="1:10" ht="312" customHeight="1">
-      <c r="A53" s="253" t="s">
+      <c r="A53" s="200" t="s">
         <v>161</v>
       </c>
       <c r="B53" s="79" t="s">
@@ -14831,13 +14831,13 @@
       <c r="H53" s="44" t="s">
         <v>244</v>
       </c>
-      <c r="I53" s="252"/>
+      <c r="I53" s="199"/>
       <c r="J53" s="48" t="s">
         <v>355</v>
       </c>
     </row>
     <row r="54" spans="1:10" ht="48" customHeight="1">
-      <c r="A54" s="253"/>
+      <c r="A54" s="200"/>
       <c r="B54" s="75" t="s">
         <v>145</v>
       </c>
@@ -14859,13 +14859,13 @@
       <c r="H54" s="44" t="s">
         <v>244</v>
       </c>
-      <c r="I54" s="252"/>
+      <c r="I54" s="199"/>
       <c r="J54" s="146" t="s">
         <v>334</v>
       </c>
     </row>
     <row r="55" spans="1:10" ht="96" customHeight="1">
-      <c r="A55" s="253"/>
+      <c r="A55" s="200"/>
       <c r="B55" s="79" t="s">
         <v>105</v>
       </c>
@@ -14875,13 +14875,13 @@
       <c r="F55" s="44"/>
       <c r="G55" s="44"/>
       <c r="H55" s="44"/>
-      <c r="I55" s="252"/>
+      <c r="I55" s="199"/>
       <c r="J55" s="147" t="s">
         <v>335</v>
       </c>
     </row>
     <row r="56" spans="1:10" ht="18">
-      <c r="A56" s="253"/>
+      <c r="A56" s="200"/>
       <c r="B56" s="79" t="s">
         <v>86</v>
       </c>
@@ -14891,13 +14891,13 @@
       <c r="F56" s="44"/>
       <c r="G56" s="44"/>
       <c r="H56" s="44"/>
-      <c r="I56" s="252"/>
+      <c r="I56" s="199"/>
       <c r="J56" s="145" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="57" spans="1:10" ht="18">
-      <c r="A57" s="253"/>
+      <c r="A57" s="200"/>
       <c r="B57" s="79" t="s">
         <v>87</v>
       </c>
@@ -14907,13 +14907,13 @@
       <c r="F57" s="44"/>
       <c r="G57" s="44"/>
       <c r="H57" s="44"/>
-      <c r="I57" s="252"/>
+      <c r="I57" s="199"/>
       <c r="J57" s="145" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="58" spans="1:10" ht="18">
-      <c r="A58" s="253"/>
+      <c r="A58" s="200"/>
       <c r="B58" s="79" t="s">
         <v>88</v>
       </c>
@@ -14923,13 +14923,13 @@
       <c r="F58" s="44"/>
       <c r="G58" s="44"/>
       <c r="H58" s="44"/>
-      <c r="I58" s="252"/>
+      <c r="I58" s="199"/>
       <c r="J58" s="145" t="s">
         <v>151</v>
       </c>
     </row>
     <row r="59" spans="1:10" ht="18">
-      <c r="A59" s="253"/>
+      <c r="A59" s="200"/>
       <c r="B59" s="79" t="s">
         <v>89</v>
       </c>
@@ -14939,13 +14939,13 @@
       <c r="F59" s="44"/>
       <c r="G59" s="44"/>
       <c r="H59" s="44"/>
-      <c r="I59" s="252"/>
+      <c r="I59" s="199"/>
       <c r="J59" s="145" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="60" spans="1:10" ht="18">
-      <c r="A60" s="253"/>
+      <c r="A60" s="200"/>
       <c r="B60" s="79" t="s">
         <v>90</v>
       </c>
@@ -14955,13 +14955,13 @@
       <c r="F60" s="44"/>
       <c r="G60" s="44"/>
       <c r="H60" s="44"/>
-      <c r="I60" s="252"/>
+      <c r="I60" s="199"/>
       <c r="J60" s="145" t="s">
         <v>153</v>
       </c>
     </row>
     <row r="61" spans="1:10" ht="21" customHeight="1">
-      <c r="A61" s="253"/>
+      <c r="A61" s="200"/>
       <c r="B61" s="79" t="s">
         <v>91</v>
       </c>
@@ -14971,13 +14971,13 @@
       <c r="F61" s="44"/>
       <c r="G61" s="44"/>
       <c r="H61" s="44"/>
-      <c r="I61" s="252"/>
+      <c r="I61" s="199"/>
       <c r="J61" s="145" t="s">
         <v>154</v>
       </c>
     </row>
     <row r="62" spans="1:10" ht="21" customHeight="1">
-      <c r="A62" s="253"/>
+      <c r="A62" s="200"/>
       <c r="B62" s="79" t="s">
         <v>92</v>
       </c>
@@ -14987,13 +14987,13 @@
       <c r="F62" s="44"/>
       <c r="G62" s="44"/>
       <c r="H62" s="44"/>
-      <c r="I62" s="252"/>
+      <c r="I62" s="199"/>
       <c r="J62" s="145" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="63" spans="1:10" ht="18">
-      <c r="A63" s="253"/>
+      <c r="A63" s="200"/>
       <c r="B63" s="79" t="s">
         <v>108</v>
       </c>
@@ -15003,13 +15003,13 @@
       <c r="F63" s="44"/>
       <c r="G63" s="44"/>
       <c r="H63" s="44"/>
-      <c r="I63" s="252"/>
+      <c r="I63" s="199"/>
       <c r="J63" s="145" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="64" spans="1:10" ht="68.25" customHeight="1">
-      <c r="A64" s="253"/>
+      <c r="A64" s="200"/>
       <c r="B64" s="75" t="s">
         <v>10</v>
       </c>
@@ -15019,13 +15019,13 @@
       <c r="F64" s="44"/>
       <c r="G64" s="44"/>
       <c r="H64" s="44"/>
-      <c r="I64" s="252"/>
+      <c r="I64" s="199"/>
       <c r="J64" s="148" t="s">
         <v>336</v>
       </c>
     </row>
     <row r="65" spans="1:10" ht="66" customHeight="1">
-      <c r="A65" s="253"/>
+      <c r="A65" s="200"/>
       <c r="B65" s="75" t="s">
         <v>106</v>
       </c>
@@ -15035,13 +15035,13 @@
       <c r="F65" s="44"/>
       <c r="G65" s="44"/>
       <c r="H65" s="44"/>
-      <c r="I65" s="252"/>
+      <c r="I65" s="199"/>
       <c r="J65" s="149" t="s">
         <v>337</v>
       </c>
     </row>
     <row r="66" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A66" s="253"/>
+      <c r="A66" s="200"/>
       <c r="B66" s="75" t="s">
         <v>133</v>
       </c>
@@ -15051,13 +15051,13 @@
       <c r="F66" s="44"/>
       <c r="G66" s="44"/>
       <c r="H66" s="44"/>
-      <c r="I66" s="252"/>
+      <c r="I66" s="199"/>
       <c r="J66" s="145" t="s">
         <v>338</v>
       </c>
     </row>
     <row r="67" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A67" s="253"/>
+      <c r="A67" s="200"/>
       <c r="B67" s="75" t="s">
         <v>134</v>
       </c>
@@ -15067,13 +15067,13 @@
       <c r="F67" s="44"/>
       <c r="G67" s="44"/>
       <c r="H67" s="44"/>
-      <c r="I67" s="252"/>
+      <c r="I67" s="199"/>
       <c r="J67" s="145" t="s">
         <v>339</v>
       </c>
     </row>
     <row r="68" spans="1:10" ht="38.25" customHeight="1">
-      <c r="A68" s="253"/>
+      <c r="A68" s="200"/>
       <c r="B68" s="75" t="s">
         <v>135</v>
       </c>
@@ -15085,13 +15085,13 @@
       <c r="F68" s="44"/>
       <c r="G68" s="44"/>
       <c r="H68" s="44"/>
-      <c r="I68" s="252"/>
+      <c r="I68" s="199"/>
       <c r="J68" s="145" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="69" spans="1:10" ht="60" customHeight="1">
-      <c r="A69" s="253"/>
+      <c r="A69" s="200"/>
       <c r="B69" s="75" t="s">
         <v>93</v>
       </c>
@@ -15101,13 +15101,13 @@
       <c r="F69" s="44"/>
       <c r="G69" s="44"/>
       <c r="H69" s="44"/>
-      <c r="I69" s="252"/>
+      <c r="I69" s="199"/>
       <c r="J69" s="145" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="70" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A70" s="253"/>
+      <c r="A70" s="200"/>
       <c r="B70" s="75" t="s">
         <v>107</v>
       </c>
@@ -15117,13 +15117,13 @@
       <c r="F70" s="44"/>
       <c r="G70" s="44"/>
       <c r="H70" s="44"/>
-      <c r="I70" s="252"/>
+      <c r="I70" s="199"/>
       <c r="J70" s="145" t="s">
         <v>342</v>
       </c>
     </row>
     <row r="71" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A71" s="253"/>
+      <c r="A71" s="200"/>
       <c r="B71" s="75" t="s">
         <v>53</v>
       </c>
@@ -15133,13 +15133,13 @@
       <c r="F71" s="44"/>
       <c r="G71" s="44"/>
       <c r="H71" s="44"/>
-      <c r="I71" s="252"/>
+      <c r="I71" s="199"/>
       <c r="J71" s="147" t="s">
         <v>343</v>
       </c>
     </row>
     <row r="72" spans="1:10" ht="48" customHeight="1">
-      <c r="A72" s="253"/>
+      <c r="A72" s="200"/>
       <c r="B72" s="75" t="s">
         <v>94</v>
       </c>
@@ -15159,33 +15159,33 @@
       <c r="H72" s="91" t="s">
         <v>244</v>
       </c>
-      <c r="I72" s="252"/>
+      <c r="I72" s="199"/>
       <c r="J72" s="147" t="s">
         <v>344</v>
       </c>
     </row>
     <row r="73" spans="1:10" ht="27" customHeight="1">
-      <c r="A73" s="207" t="s">
+      <c r="A73" s="177" t="s">
         <v>28</v>
       </c>
-      <c r="B73" s="207"/>
-      <c r="C73" s="202"/>
-      <c r="D73" s="244" t="s">
+      <c r="B73" s="177"/>
+      <c r="C73" s="197"/>
+      <c r="D73" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="E73" s="244" t="s">
+      <c r="E73" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="F73" s="244" t="s">
+      <c r="F73" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="G73" s="244" t="s">
+      <c r="G73" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="H73" s="244" t="s">
+      <c r="H73" s="225" t="s">
         <v>5</v>
       </c>
-      <c r="I73" s="245" t="s">
+      <c r="I73" s="235" t="s">
         <v>310</v>
       </c>
       <c r="J73" s="135" t="s">
@@ -15193,94 +15193,94 @@
       </c>
     </row>
     <row r="74" spans="1:10" ht="27" customHeight="1">
-      <c r="A74" s="207"/>
-      <c r="B74" s="207"/>
-      <c r="C74" s="202"/>
-      <c r="D74" s="244"/>
-      <c r="E74" s="244"/>
-      <c r="F74" s="244"/>
-      <c r="G74" s="244"/>
-      <c r="H74" s="244"/>
-      <c r="I74" s="245"/>
+      <c r="A74" s="177"/>
+      <c r="B74" s="177"/>
+      <c r="C74" s="197"/>
+      <c r="D74" s="225"/>
+      <c r="E74" s="225"/>
+      <c r="F74" s="225"/>
+      <c r="G74" s="225"/>
+      <c r="H74" s="225"/>
+      <c r="I74" s="235"/>
       <c r="J74" s="150" t="s">
         <v>345</v>
       </c>
     </row>
     <row r="75" spans="1:10" ht="27" customHeight="1">
-      <c r="A75" s="207"/>
-      <c r="B75" s="207"/>
-      <c r="C75" s="202"/>
-      <c r="D75" s="244"/>
-      <c r="E75" s="244"/>
-      <c r="F75" s="244"/>
-      <c r="G75" s="244"/>
-      <c r="H75" s="244"/>
-      <c r="I75" s="245"/>
+      <c r="A75" s="177"/>
+      <c r="B75" s="177"/>
+      <c r="C75" s="197"/>
+      <c r="D75" s="225"/>
+      <c r="E75" s="225"/>
+      <c r="F75" s="225"/>
+      <c r="G75" s="225"/>
+      <c r="H75" s="225"/>
+      <c r="I75" s="235"/>
       <c r="J75" s="135" t="s">
         <v>54</v>
       </c>
     </row>
     <row r="76" spans="1:10" ht="27" customHeight="1">
-      <c r="A76" s="207"/>
-      <c r="B76" s="207"/>
-      <c r="C76" s="202"/>
-      <c r="D76" s="244"/>
-      <c r="E76" s="244"/>
-      <c r="F76" s="244"/>
-      <c r="G76" s="244"/>
-      <c r="H76" s="244"/>
-      <c r="I76" s="245"/>
+      <c r="A76" s="177"/>
+      <c r="B76" s="177"/>
+      <c r="C76" s="197"/>
+      <c r="D76" s="225"/>
+      <c r="E76" s="225"/>
+      <c r="F76" s="225"/>
+      <c r="G76" s="225"/>
+      <c r="H76" s="225"/>
+      <c r="I76" s="235"/>
       <c r="J76" s="150" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="77" spans="1:10" ht="27" customHeight="1">
-      <c r="A77" s="207"/>
-      <c r="B77" s="207"/>
-      <c r="C77" s="202"/>
-      <c r="D77" s="244"/>
-      <c r="E77" s="244"/>
-      <c r="F77" s="244"/>
-      <c r="G77" s="244"/>
-      <c r="H77" s="244"/>
-      <c r="I77" s="245"/>
+      <c r="A77" s="177"/>
+      <c r="B77" s="177"/>
+      <c r="C77" s="197"/>
+      <c r="D77" s="225"/>
+      <c r="E77" s="225"/>
+      <c r="F77" s="225"/>
+      <c r="G77" s="225"/>
+      <c r="H77" s="225"/>
+      <c r="I77" s="235"/>
       <c r="J77" s="135" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="78" spans="1:10" ht="27" customHeight="1">
-      <c r="A78" s="207"/>
-      <c r="B78" s="207"/>
-      <c r="C78" s="202"/>
-      <c r="D78" s="244"/>
-      <c r="E78" s="244"/>
-      <c r="F78" s="244"/>
-      <c r="G78" s="244"/>
-      <c r="H78" s="244"/>
-      <c r="I78" s="245"/>
+      <c r="A78" s="177"/>
+      <c r="B78" s="177"/>
+      <c r="C78" s="197"/>
+      <c r="D78" s="225"/>
+      <c r="E78" s="225"/>
+      <c r="F78" s="225"/>
+      <c r="G78" s="225"/>
+      <c r="H78" s="225"/>
+      <c r="I78" s="235"/>
       <c r="J78" s="150" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="79" spans="1:10" ht="45.75" customHeight="1">
-      <c r="A79" s="207"/>
-      <c r="B79" s="207"/>
-      <c r="C79" s="202"/>
-      <c r="D79" s="244"/>
-      <c r="E79" s="244"/>
-      <c r="F79" s="244"/>
-      <c r="G79" s="244"/>
-      <c r="H79" s="244"/>
-      <c r="I79" s="245"/>
+      <c r="A79" s="177"/>
+      <c r="B79" s="177"/>
+      <c r="C79" s="197"/>
+      <c r="D79" s="225"/>
+      <c r="E79" s="225"/>
+      <c r="F79" s="225"/>
+      <c r="G79" s="225"/>
+      <c r="H79" s="225"/>
+      <c r="I79" s="235"/>
       <c r="J79" s="135" t="s">
         <v>311</v>
       </c>
     </row>
     <row r="80" spans="1:10" ht="100.5" customHeight="1">
-      <c r="A80" s="207" t="s">
+      <c r="A80" s="177" t="s">
         <v>35</v>
       </c>
-      <c r="B80" s="207"/>
+      <c r="B80" s="177"/>
       <c r="C80" s="74"/>
       <c r="D80" s="24" t="s">
         <v>0</v>
@@ -15305,10 +15305,10 @@
       </c>
     </row>
     <row r="81" spans="1:10" ht="105.75" customHeight="1">
-      <c r="A81" s="207" t="s">
+      <c r="A81" s="177" t="s">
         <v>46</v>
       </c>
-      <c r="B81" s="207"/>
+      <c r="B81" s="177"/>
       <c r="C81" s="74" t="s">
         <v>47</v>
       </c>
@@ -15347,13 +15347,13 @@
       <c r="J82" s="11"/>
     </row>
     <row r="83" spans="1:10" ht="65.25" customHeight="1">
-      <c r="A83" s="207" t="s">
+      <c r="A83" s="177" t="s">
         <v>59</v>
       </c>
       <c r="B83" s="73" t="s">
         <v>60</v>
       </c>
-      <c r="C83" s="228" t="s">
+      <c r="C83" s="232" t="s">
         <v>78</v>
       </c>
       <c r="D83" s="91" t="s">
@@ -15379,24 +15379,24 @@
       </c>
     </row>
     <row r="84" spans="1:10" ht="108">
-      <c r="A84" s="207"/>
-      <c r="B84" s="207" t="s">
+      <c r="A84" s="177"/>
+      <c r="B84" s="177" t="s">
         <v>64</v>
       </c>
-      <c r="C84" s="228"/>
-      <c r="D84" s="199" t="s">
+      <c r="C84" s="232"/>
+      <c r="D84" s="175" t="s">
         <v>241</v>
       </c>
-      <c r="E84" s="199" t="s">
+      <c r="E84" s="175" t="s">
         <v>241</v>
       </c>
-      <c r="F84" s="199" t="s">
+      <c r="F84" s="175" t="s">
         <v>241</v>
       </c>
-      <c r="G84" s="199" t="s">
+      <c r="G84" s="175" t="s">
         <v>241</v>
       </c>
-      <c r="H84" s="194" t="s">
+      <c r="H84" s="176" t="s">
         <v>62</v>
       </c>
       <c r="I84" s="104" t="s">
@@ -15407,14 +15407,14 @@
       </c>
     </row>
     <row r="85" spans="1:10" ht="49.5" customHeight="1">
-      <c r="A85" s="207"/>
-      <c r="B85" s="207"/>
-      <c r="C85" s="228"/>
-      <c r="D85" s="199"/>
-      <c r="E85" s="199"/>
-      <c r="F85" s="199"/>
-      <c r="G85" s="199"/>
-      <c r="H85" s="194"/>
+      <c r="A85" s="177"/>
+      <c r="B85" s="177"/>
+      <c r="C85" s="232"/>
+      <c r="D85" s="175"/>
+      <c r="E85" s="175"/>
+      <c r="F85" s="175"/>
+      <c r="G85" s="175"/>
+      <c r="H85" s="176"/>
       <c r="I85" s="104" t="s">
         <v>67</v>
       </c>
@@ -15423,7 +15423,7 @@
       </c>
     </row>
     <row r="86" spans="1:10" ht="48" customHeight="1">
-      <c r="A86" s="207" t="s">
+      <c r="A86" s="177" t="s">
         <v>69</v>
       </c>
       <c r="B86" s="73" t="s">
@@ -15447,15 +15447,15 @@
       <c r="H86" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="I86" s="208" t="s">
+      <c r="I86" s="178" t="s">
         <v>104</v>
       </c>
-      <c r="J86" s="283" t="s">
+      <c r="J86" s="179" t="s">
         <v>349</v>
       </c>
     </row>
     <row r="87" spans="1:10" ht="47.25" customHeight="1">
-      <c r="A87" s="207"/>
+      <c r="A87" s="177"/>
       <c r="B87" s="73" t="s">
         <v>72</v>
       </c>
@@ -15477,8 +15477,8 @@
       <c r="H87" s="102" t="s">
         <v>62</v>
       </c>
-      <c r="I87" s="208"/>
-      <c r="J87" s="284"/>
+      <c r="I87" s="178"/>
+      <c r="J87" s="180"/>
     </row>
     <row r="90" spans="1:10" hidden="1">
       <c r="A90" s="12" t="s">
@@ -15488,35 +15488,35 @@
       <c r="C90" s="1"/>
     </row>
     <row r="91" spans="1:10" ht="39.75" hidden="1" customHeight="1">
-      <c r="A91" s="238" t="s">
+      <c r="A91" s="205" t="s">
         <v>22</v>
       </c>
-      <c r="B91" s="238"/>
-      <c r="C91" s="238" t="s">
+      <c r="B91" s="205"/>
+      <c r="C91" s="205" t="s">
         <v>6</v>
       </c>
-      <c r="D91" s="249" t="s">
+      <c r="D91" s="224" t="s">
         <v>7</v>
       </c>
-      <c r="E91" s="249"/>
-      <c r="F91" s="249" t="s">
+      <c r="E91" s="224"/>
+      <c r="F91" s="224" t="s">
         <v>8</v>
       </c>
-      <c r="G91" s="249"/>
-      <c r="H91" s="250" t="s">
+      <c r="G91" s="224"/>
+      <c r="H91" s="216" t="s">
         <v>9</v>
       </c>
-      <c r="I91" s="238" t="s">
+      <c r="I91" s="205" t="s">
         <v>2</v>
       </c>
-      <c r="J91" s="238" t="s">
+      <c r="J91" s="205" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="92" spans="1:10" ht="39.75" hidden="1" customHeight="1">
-      <c r="A92" s="238"/>
-      <c r="B92" s="238"/>
-      <c r="C92" s="238"/>
+      <c r="A92" s="205"/>
+      <c r="B92" s="205"/>
+      <c r="C92" s="205"/>
       <c r="D92" s="6" t="s">
         <v>3</v>
       </c>
@@ -15529,18 +15529,18 @@
       <c r="G92" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="H92" s="250"/>
-      <c r="I92" s="238"/>
-      <c r="J92" s="238"/>
+      <c r="H92" s="216"/>
+      <c r="I92" s="205"/>
+      <c r="J92" s="205"/>
     </row>
     <row r="93" spans="1:10" ht="91.5" hidden="1" customHeight="1">
-      <c r="A93" s="236" t="s">
+      <c r="A93" s="217" t="s">
         <v>59</v>
       </c>
       <c r="B93" s="19" t="s">
         <v>98</v>
       </c>
-      <c r="C93" s="179" t="s">
+      <c r="C93" s="220" t="s">
         <v>99</v>
       </c>
       <c r="D93" s="19" t="s">
@@ -15558,7 +15558,7 @@
       <c r="H93" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="I93" s="181" t="s">
+      <c r="I93" s="222" t="s">
         <v>100</v>
       </c>
       <c r="J93" s="18" t="s">
@@ -15566,11 +15566,11 @@
       </c>
     </row>
     <row r="94" spans="1:10" ht="124.5" hidden="1" customHeight="1">
-      <c r="A94" s="239"/>
+      <c r="A94" s="218"/>
       <c r="B94" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="C94" s="180"/>
+      <c r="C94" s="221"/>
       <c r="D94" s="23" t="s">
         <v>5</v>
       </c>
@@ -15586,13 +15586,13 @@
       <c r="H94" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="I94" s="182"/>
+      <c r="I94" s="223"/>
       <c r="J94" s="22" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="95" spans="1:10" ht="91.5" hidden="1" customHeight="1">
-      <c r="A95" s="237"/>
+      <c r="A95" s="219"/>
       <c r="B95" s="28" t="s">
         <v>114</v>
       </c>
@@ -15622,10 +15622,10 @@
       </c>
     </row>
     <row r="96" spans="1:10" ht="246.75" hidden="1" customHeight="1">
-      <c r="A96" s="244" t="s">
+      <c r="A96" s="225" t="s">
         <v>50</v>
       </c>
-      <c r="B96" s="244"/>
+      <c r="B96" s="225"/>
       <c r="C96" s="25"/>
       <c r="D96" s="24"/>
       <c r="E96" s="24"/>
@@ -16112,6 +16112,122 @@
     <filterColumn colId="0" showButton="0"/>
   </autoFilter>
   <mergeCells count="140">
+    <mergeCell ref="A81:B81"/>
+    <mergeCell ref="A73:B79"/>
+    <mergeCell ref="C73:C79"/>
+    <mergeCell ref="D73:D79"/>
+    <mergeCell ref="E73:E79"/>
+    <mergeCell ref="F73:F79"/>
+    <mergeCell ref="G73:G79"/>
+    <mergeCell ref="I23:I24"/>
+    <mergeCell ref="A25:B29"/>
+    <mergeCell ref="C28:C29"/>
+    <mergeCell ref="D28:D29"/>
+    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="I28:I29"/>
+    <mergeCell ref="C26:C27"/>
+    <mergeCell ref="D26:D27"/>
+    <mergeCell ref="E26:E27"/>
+    <mergeCell ref="F26:F27"/>
+    <mergeCell ref="A23:B24"/>
+    <mergeCell ref="C23:C24"/>
+    <mergeCell ref="D23:D24"/>
+    <mergeCell ref="A39:B40"/>
+    <mergeCell ref="C39:C40"/>
+    <mergeCell ref="I39:I40"/>
+    <mergeCell ref="G26:G27"/>
+    <mergeCell ref="H26:H27"/>
+    <mergeCell ref="G21:G22"/>
+    <mergeCell ref="H15:H16"/>
+    <mergeCell ref="I15:I16"/>
+    <mergeCell ref="A1:J2"/>
+    <mergeCell ref="H73:H79"/>
+    <mergeCell ref="I73:I79"/>
+    <mergeCell ref="A80:B80"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A18:B18"/>
+    <mergeCell ref="A19:B20"/>
+    <mergeCell ref="C19:C20"/>
+    <mergeCell ref="D19:D20"/>
+    <mergeCell ref="E19:E20"/>
+    <mergeCell ref="F19:F20"/>
+    <mergeCell ref="H21:H22"/>
+    <mergeCell ref="E23:E24"/>
+    <mergeCell ref="F23:F24"/>
+    <mergeCell ref="G23:G24"/>
+    <mergeCell ref="H23:H24"/>
+    <mergeCell ref="D49:D52"/>
+    <mergeCell ref="E49:E52"/>
+    <mergeCell ref="F49:F52"/>
+    <mergeCell ref="G49:G52"/>
+    <mergeCell ref="A96:B96"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="A11:B14"/>
+    <mergeCell ref="C11:C14"/>
+    <mergeCell ref="D11:D14"/>
+    <mergeCell ref="E11:E14"/>
+    <mergeCell ref="A30:B31"/>
+    <mergeCell ref="C30:C31"/>
+    <mergeCell ref="D30:D31"/>
+    <mergeCell ref="E30:E31"/>
+    <mergeCell ref="D41:D43"/>
+    <mergeCell ref="E41:E43"/>
+    <mergeCell ref="A32:B33"/>
+    <mergeCell ref="C32:C33"/>
+    <mergeCell ref="A83:A85"/>
+    <mergeCell ref="C83:C85"/>
+    <mergeCell ref="B84:B85"/>
+    <mergeCell ref="D84:D85"/>
+    <mergeCell ref="E84:E85"/>
+    <mergeCell ref="A15:B16"/>
+    <mergeCell ref="C15:C16"/>
+    <mergeCell ref="D15:D16"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="A21:B22"/>
+    <mergeCell ref="H91:H92"/>
+    <mergeCell ref="I91:I92"/>
+    <mergeCell ref="J91:J92"/>
+    <mergeCell ref="A93:A95"/>
+    <mergeCell ref="C93:C94"/>
+    <mergeCell ref="I93:I94"/>
+    <mergeCell ref="A91:B92"/>
+    <mergeCell ref="C91:C92"/>
+    <mergeCell ref="D91:E91"/>
+    <mergeCell ref="F91:G91"/>
+    <mergeCell ref="H49:H52"/>
+    <mergeCell ref="I44:I46"/>
+    <mergeCell ref="A47:B48"/>
+    <mergeCell ref="C47:C48"/>
+    <mergeCell ref="D47:D48"/>
+    <mergeCell ref="E47:E48"/>
+    <mergeCell ref="F47:F48"/>
+    <mergeCell ref="G47:G48"/>
+    <mergeCell ref="H47:H48"/>
+    <mergeCell ref="I47:I48"/>
+    <mergeCell ref="I30:I31"/>
+    <mergeCell ref="I26:I27"/>
+    <mergeCell ref="A8:B9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:E8"/>
+    <mergeCell ref="F8:G8"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="I8:I9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="F11:F14"/>
+    <mergeCell ref="G11:G14"/>
+    <mergeCell ref="H11:H14"/>
+    <mergeCell ref="I11:I14"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="G15:G16"/>
+    <mergeCell ref="I19:I20"/>
+    <mergeCell ref="J19:J20"/>
+    <mergeCell ref="C21:C22"/>
+    <mergeCell ref="D21:D22"/>
+    <mergeCell ref="E21:E22"/>
+    <mergeCell ref="F21:F22"/>
+    <mergeCell ref="G19:G20"/>
+    <mergeCell ref="H19:H20"/>
+    <mergeCell ref="J15:J16"/>
     <mergeCell ref="F84:F85"/>
     <mergeCell ref="G84:G85"/>
     <mergeCell ref="H84:H85"/>
@@ -16136,122 +16252,6 @@
     <mergeCell ref="I49:I72"/>
     <mergeCell ref="A53:A72"/>
     <mergeCell ref="A49:A52"/>
-    <mergeCell ref="I30:I31"/>
-    <mergeCell ref="I26:I27"/>
-    <mergeCell ref="A8:B9"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="D8:E8"/>
-    <mergeCell ref="F8:G8"/>
-    <mergeCell ref="H8:H9"/>
-    <mergeCell ref="I8:I9"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="F11:F14"/>
-    <mergeCell ref="G11:G14"/>
-    <mergeCell ref="H11:H14"/>
-    <mergeCell ref="I11:I14"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="G15:G16"/>
-    <mergeCell ref="I19:I20"/>
-    <mergeCell ref="J19:J20"/>
-    <mergeCell ref="C21:C22"/>
-    <mergeCell ref="D21:D22"/>
-    <mergeCell ref="E21:E22"/>
-    <mergeCell ref="F21:F22"/>
-    <mergeCell ref="G19:G20"/>
-    <mergeCell ref="H19:H20"/>
-    <mergeCell ref="J15:J16"/>
-    <mergeCell ref="H49:H52"/>
-    <mergeCell ref="I44:I46"/>
-    <mergeCell ref="A47:B48"/>
-    <mergeCell ref="C47:C48"/>
-    <mergeCell ref="D47:D48"/>
-    <mergeCell ref="E47:E48"/>
-    <mergeCell ref="F47:F48"/>
-    <mergeCell ref="G47:G48"/>
-    <mergeCell ref="H47:H48"/>
-    <mergeCell ref="I47:I48"/>
-    <mergeCell ref="H91:H92"/>
-    <mergeCell ref="I91:I92"/>
-    <mergeCell ref="J91:J92"/>
-    <mergeCell ref="A93:A95"/>
-    <mergeCell ref="C93:C94"/>
-    <mergeCell ref="I93:I94"/>
-    <mergeCell ref="A91:B92"/>
-    <mergeCell ref="C91:C92"/>
-    <mergeCell ref="D91:E91"/>
-    <mergeCell ref="F91:G91"/>
-    <mergeCell ref="A96:B96"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="A11:B14"/>
-    <mergeCell ref="C11:C14"/>
-    <mergeCell ref="D11:D14"/>
-    <mergeCell ref="E11:E14"/>
-    <mergeCell ref="A30:B31"/>
-    <mergeCell ref="C30:C31"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="D41:D43"/>
-    <mergeCell ref="E41:E43"/>
-    <mergeCell ref="A32:B33"/>
-    <mergeCell ref="C32:C33"/>
-    <mergeCell ref="A83:A85"/>
-    <mergeCell ref="C83:C85"/>
-    <mergeCell ref="B84:B85"/>
-    <mergeCell ref="D84:D85"/>
-    <mergeCell ref="E84:E85"/>
-    <mergeCell ref="A15:B16"/>
-    <mergeCell ref="C15:C16"/>
-    <mergeCell ref="D15:D16"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="A21:B22"/>
-    <mergeCell ref="H26:H27"/>
-    <mergeCell ref="G21:G22"/>
-    <mergeCell ref="H15:H16"/>
-    <mergeCell ref="I15:I16"/>
-    <mergeCell ref="A1:J2"/>
-    <mergeCell ref="H73:H79"/>
-    <mergeCell ref="I73:I79"/>
-    <mergeCell ref="A80:B80"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A18:B18"/>
-    <mergeCell ref="A19:B20"/>
-    <mergeCell ref="C19:C20"/>
-    <mergeCell ref="D19:D20"/>
-    <mergeCell ref="E19:E20"/>
-    <mergeCell ref="F19:F20"/>
-    <mergeCell ref="H21:H22"/>
-    <mergeCell ref="E23:E24"/>
-    <mergeCell ref="F23:F24"/>
-    <mergeCell ref="G23:G24"/>
-    <mergeCell ref="H23:H24"/>
-    <mergeCell ref="D49:D52"/>
-    <mergeCell ref="E49:E52"/>
-    <mergeCell ref="F49:F52"/>
-    <mergeCell ref="G49:G52"/>
-    <mergeCell ref="A81:B81"/>
-    <mergeCell ref="A73:B79"/>
-    <mergeCell ref="C73:C79"/>
-    <mergeCell ref="D73:D79"/>
-    <mergeCell ref="E73:E79"/>
-    <mergeCell ref="F73:F79"/>
-    <mergeCell ref="G73:G79"/>
-    <mergeCell ref="I23:I24"/>
-    <mergeCell ref="A25:B29"/>
-    <mergeCell ref="C28:C29"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="E28:E29"/>
-    <mergeCell ref="I28:I29"/>
-    <mergeCell ref="C26:C27"/>
-    <mergeCell ref="D26:D27"/>
-    <mergeCell ref="E26:E27"/>
-    <mergeCell ref="F26:F27"/>
-    <mergeCell ref="A23:B24"/>
-    <mergeCell ref="C23:C24"/>
-    <mergeCell ref="D23:D24"/>
-    <mergeCell ref="A39:B40"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="I39:I40"/>
-    <mergeCell ref="G26:G27"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
